--- a/tasks/image-captioning/qwen-qwen3-5-9b/results.xlsx
+++ b/tasks/image-captioning/qwen-qwen3-5-9b/results.xlsx
@@ -16,10 +16,10 @@
     <sheet name="Judges" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$B$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Metrics'!$A$1:$B$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$B$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Metrics'!$A$1:$B$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Rubric'!$A$1:$F$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sample'!$A$1:$V$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sample'!$A$1:$V$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Sample Rows'!$A$1:$B$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Samples'!$A$1:$U$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Judges'!$A$1:$J$61</definedName>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -523,7 +523,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.2515</t>
+          <t>0.2506</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.1511</t>
+          <t>0.1508</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
@@ -619,7 +619,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The model generally provides accurate descriptions of images but occasionally introduces minor inaccuracies or hallucinations, particularly in details like object orientations, specific text, and structural elements, without a clear recurring edge case.</t>
+          <t>The model demonstrates inconsistent accuracy in image captioning, occasionally introducing hallucinations such as incorrect structures or object details, but does not exhibit a clear recurring edge case across the samples.</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'name': 'NVIDIA A100-SXM4-40GB', 'total_vram_gb': 39.49, 'peak_vram_allocated_gb': 0.0, 'cuda': '12.8'} (0.0 GB peak)</t>
+          <t>NVIDIA A100-SXM4-40GB (34.25 GB)</t>
         </is>
       </c>
     </row>
@@ -707,8 +707,124 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Definitions</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>term</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>llm_judge_dimension_mean_0_to_5</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>For each sample, each valid LLM judge scores every graded rubric dimension from 0 to 5. The scorer averages judges per dimension, averages those graded dimensions into a sample score, then averages sample scores across the run. Binary gates such as Safety and Faithfulness are not included in this mean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>llm_judge_pass_rate</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>The fraction of samples whose LLM-judge consensus passed: dimension mean is at least 3.0, no graded dimension is 0 or 1, and all binary/ranged gates pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>model_supported_languages</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Languages claimed by the model card or model metadata. If the model card describes broad support without enumerating every language, the workbook keeps the concise claim, such as 'over 140 languages'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>eval_languages</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Languages covered by this evaluation task or dataset. This is provenance for the run, not the full language capability of the model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>inference_time</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Performance headline latency. For remote third-party APIs this is the client-observed p50 end-to-end latency from the natural task run, normally at concurrency 1; it includes provider routing, queueing, network, image preprocessing, and model inference. For self-hosted Colab GPU runs it is GPU-only inference latency (no network/provider overhead).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>hardware</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>The hardware the performance timing was measured on. For self-hosted Colab runs this is the exact GPU (name and peak VRAM), pinned across models for comparability. For remote third-party APIs it records that the measurement was client-observed, since the serving hardware is not exposed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>token_f1</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Token-level F1 between the model output and the reference: treats each as a bag of lowercased word tokens and computes the harmonic mean of precision (fraction of output tokens found in the reference) and recall (fraction of reference tokens found in the output). Ranges 0 to 1; order-insensitive, so it rewards content overlap rather than exact phrasing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>rouge_l</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ROUGE-L F1 based on the longest common subsequence (LCS) between output and reference token sequences. Unlike token_f1 it respects word order (the LCS must appear in sequence), so it credits fluent, correctly-ordered overlap. Ranges 0 to 1.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B22"/>
+  <autoFilter ref="A1:B33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -719,7 +835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -746,7 +862,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.2515</t>
+          <t>0.2506</t>
         </is>
       </c>
     </row>
@@ -758,7 +874,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.1511</t>
+          <t>0.1508</t>
         </is>
       </c>
     </row>
@@ -770,7 +886,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.3064</t>
+          <t>0.3067</t>
         </is>
       </c>
     </row>
@@ -782,7 +898,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.1643</t>
+          <t>1.189</t>
         </is>
       </c>
     </row>
@@ -794,7 +910,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.8135</t>
+          <t>0.8125</t>
         </is>
       </c>
     </row>
@@ -806,7 +922,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.7072</t>
+          <t>0.7134</t>
         </is>
       </c>
     </row>
@@ -830,7 +946,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
@@ -881,149 +997,77 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>dataset_seed</t>
+          <t>token_f1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The deterministic sampling seed used to choose dataset rows for the frozen sample. It controls which examples are selected for the eval so every model sees the same rows for the same dataset/config/sample count; it is not a model generation seed.</t>
+          <t>Token-level F1 between the model output and the reference: treats each as a bag of lowercased word tokens and computes the harmonic mean of precision (fraction of output tokens found in the reference) and recall (fraction of reference tokens found in the output). Ranges 0 to 1; order-insensitive, so it rewards content overlap rather than exact phrasing.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sample_id</t>
+          <t>rouge_l</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A short hash of the frozen sample definition and selected dataset rows. Matching sample IDs mean runs are using the same frozen sample.</t>
+          <t>ROUGE-L F1 based on the longest common subsequence (LCS) between output and reference token sequences. Unlike token_f1 it respects word order (the LCS must appear in sequence), so it credits fluent, correctly-ordered overlap. Ranges 0 to 1.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>model_supported_languages</t>
+          <t>meteor</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Languages claimed by the model card or model metadata. If the model card describes broad support without enumerating every language, the workbook keeps the concise claim, such as 'over 140 languages'.</t>
+          <t>METEOR score (via NLTK) aligning output and reference tokens with exact, stem, and synonym matches, then penalising fragmented word order. Ranges 0 to 1; correlates better with human judgement than pure n-gram overlap. Null if the NLTK/WordNet data is unavailable in the run image.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>eval_languages</t>
+          <t>cider</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Languages covered by this evaluation task or dataset. This is provenance for the run, not the full language capability of the model.</t>
+          <t>CIDEr — corpus-level consensus metric for captioning: TF-IDF-weighted n-gram (n=1..4) cosine similarity between each output and its reference(s), rewarding informative n-grams and down-weighting common ones. Computed over the whole run, not per sample.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>inference_time</t>
+          <t>bertscore</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Performance headline latency. For remote third-party APIs this is the client-observed p50 end-to-end latency from the natural task run, normally at concurrency 1; it includes provider routing, queueing, network, image preprocessing, and model inference. For self-hosted Colab GPU runs it is GPU-only inference latency (no network/provider overhead).</t>
+          <t>BERTScore F1 — token embedding similarity from a RoBERTa model rather than surface overlap, so it credits paraphrases and semantically equivalent wording. Ranges roughly 0 to 1. Heavy (needs torch + the model); null when those deps/models are absent from the run image.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>hardware</t>
+          <t>clipscore</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The hardware the performance timing was measured on. For self-hosted Colab runs this is the exact GPU (name and peak VRAM), pinned across models for comparability. For remote third-party APIs it records that the measurement was client-observed, since the serving hardware is not exposed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>token_f1</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Token-level F1 between the model output and the reference: treats each as a bag of lowercased word tokens and computes the harmonic mean of precision (fraction of output tokens found in the reference) and recall (fraction of reference tokens found in the output). Ranges 0 to 1; order-insensitive, so it rewards content overlap rather than exact phrasing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>rouge_l</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>ROUGE-L F1 based on the longest common subsequence (LCS) between output and reference token sequences. Unlike token_f1 it respects word order (the LCS must appear in sequence), so it credits fluent, correctly-ordered overlap. Ranges 0 to 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>meteor</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>METEOR score (via NLTK) aligning output and reference tokens with exact, stem, and synonym matches, then penalising fragmented word order. Ranges 0 to 1; correlates better with human judgement than pure n-gram overlap. Null if the NLTK/WordNet data is unavailable in the run image.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>cider</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>CIDEr — corpus-level consensus metric for captioning: TF-IDF-weighted n-gram (n=1..4) cosine similarity between each output and its reference(s), rewarding informative n-grams and down-weighting common ones. Computed over the whole run, not per sample.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>bertscore</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>BERTScore F1 — token embedding similarity from a RoBERTa model rather than surface overlap, so it credits paraphrases and semantically equivalent wording. Ranges roughly 0 to 1. Heavy (needs torch + the model); null when those deps/models are absent from the run image.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>clipscore</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
           <t>CLIPScore — reference-FREE image-caption alignment: cosine similarity between the caption's text embedding and the image's embedding from a CLIP model. Measures how well the caption matches the actual image (not a reference caption). Heavy (needs torch + CLIP); null when unavailable or when no image is present.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B26"/>
+  <autoFilter ref="A1:B20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1921,11 +1965,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -2252,8 +2296,52 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Definitions</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>term</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>dataset_seed</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>The deterministic sampling seed used to choose dataset rows for the frozen sample. It controls which examples are selected for the eval so every model sees the same rows for the same dataset/config/sample count; it is not a model generation seed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sample_id</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>A short hash of the frozen sample definition and selected dataset rows. Matching sample IDs mean runs are using the same frozen sample.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V3"/>
+  <autoFilter ref="A1:V8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2693,31 +2781,37 @@
         <is>
           <t>Thinking: The user wants a detailed description of the image.
 1.  **Identify the main subject:** The central focus is a small, black solar-powered garden light standing in a patch of dirt next to a concrete path.
-2.  **Describe the lighting effect:** The light is on, casting a distinct starburst pattern of light and shadow across the concrete surface. The rays emanate from the light source, creating a radial pattern.
+2.  **Describe the lighting effect:** The light is on, casting a distinct, starburst-like pattern of light and shadow across the concrete surface. The rays emanate from the light source, creating a radial pattern.
 3.  **Describe the setting:**
     *   **Foreground/Left:** A concrete walkway or driveway. It's grey and textured.
-    *   **Middle/Right:** A garden bed with dark soil, some sparse grass, and a few small plants.
-    *   **Bottom Right:** A low concrete curb separating the path from the garden bed. Next to it are some rough, light-colored rocks or stones.
-    *   **Top Right:** A bush with dark green leaves and small purple/blue flowers.
-4.  **Identify specific details:**
-    *   **The Light:** It has a black, dome-shaped top (solar panel) and a thin metal stake.
-    *   **The Manhole Cover:** There is a circular metal cover embedded in the soil near the light. It has text on it, partially legible as "METRO" and "SEWER". It has a star design in the center.
-    *   **Other lights:** There's a faint glow of another light source in the top right corner, near the bush.
-    *   **Shadows:** The shadows are sharp and distinct, indicating a strong point source of light.
-5.  **Structure the description:**
-    *   Start with the main subject (the light and its effect).
-    *   Move to the immediate surroundings (the manhole cover, the curb).
-    *   Describe the background elements (the bush, the other light).
-    *   Mention the lighting and atmosphere (nighttime, artificial light).
-**Drafting the description:**
-A small, black solar garden light stands in a patch of dark soil next to a concrete walkway, casting a dramatic starburst pattern of light and shadow across the pavement. The light source, positioned centrally, emits a warm, yellowish glow that radiates outward in distinct rays, illuminating the grey concrete surface to the left. To the right of the light, embedded in the dirt, is a circular metal utility cover, likely a sewer access point, featuring a star design and the word "METRO" visible on its surface. A low concrete curb separates the walkway from the garden bed, where sparse grass and a few small plants grow. In the bottom right corner, rough, light-colored rocks are piled up. Further back in the top right corner, a dark green bush with small purple flowers is visible, illuminated by a secondary, fainter light source near the top edge. The scene is set at night, with the primary illumination coming from the single garden light, creating high contrast between the bright rays and the surrounding darkness.
-**Refining:**
-*   Make sure to mention the specific text on the manhole cover if possible. It looks like "METRO" and "SEWER".
-*   Clarify the spatial relationship: light is between the path and the garden bed.
-*   Ensure the "starburst" effect is described clearly.
-**Final Polish:**
-A small, black solar-powered garden light stands in a patch of dark earth next to a concrete walkway, casting a distinct starburst pattern of light and shadow across the pavement. The light, which has a dome-shaped top and a thin metal stake, emits a warm, yellowish glow that radiates outward in sharp rays, illuminating the grey concrete surface to the left. To the right of the light, embedded in the soil, is a circular metal utility cover featuring a star design and the text "METRO" and "SEWER" visible on its surface. A low concrete curb runs diagonally from the bottom center towards the right, separating the walkway from the garden bed. In the bottom right corner, a pile of rough, light-colored rocks sits near the curb. In the upper right background, a dark green bush with small purple flowers is partially visible, illuminated by a fainter light source near the top edge. The scene is captured at night, emphasizing the contrast between the bright, radial light pattern and the surrounding darkness.
-A small, black solar-powered garden light stands in a patch of dark earth next to a concrete walkway, casting a distinct starburst pattern of light and shadow across the pavement. The light, which has a dome-shaped top and a thin metal stake, emits a warm, yellowish glow that radiates outward in sharp rays, illuminating the grey concrete surface to the left. To the right of the light, embedded in the soil, is a circular metal utility cover featuring a star design and the text "METRO" and "</t>
+    *   **Middle/Right:** A patch of dark soil/mulch.
+    *   **Right edge:** A low concrete curb separates the path from the soil.
+    *   **Far right:** Some rocks and a bush/plant with dark leaves.
+    *   **In the soil:** There is a round, metallic utility cover (looks like a gas or water meter cover) with embossed text.
+4.  **Details on the utility cover:** It's copper or bronze-colored. Text is visible but slightly blurry. I can make out "METER" and some stars.
+5.  **Details on the light:** It has a black dome top and a thin metal stake.
+6.  **Lighting/Atmosphere:** It's nighttime. The scene is illuminated primarily by the garden light itself, creating high contrast between the bright light rays and the dark shadows.
+7.  **Secondary elements:**
+    *   Another small light fixture is visible in the upper right corner, partially cut off.
+    *   A small, dark object (maybe another light or sensor) is in the dirt near the utility cover.
+    *   The concrete curb runs diagonally from the bottom center towards the right.
+**Drafting the description (mental outline):**
+Start with the light and its effect. Mention the concrete path. Describe the dirt area with the utility cover. Mention the curb and the plants/rocks. Note the time of day (night).
+**Refining the description:**
+*   "A small, black solar garden light stands in a patch of dark soil..."
+*   "...casting a radial pattern of bright, starburst-like rays across a grey concrete walkway."
+*   "The light is positioned near a low concrete curb that separates the path from the garden bed."
+*   "In the soil, to the right of the light, lies a round, bronze-colored utility meter cover with embossed text and stars."
+*   "To the far right, there are rough, light-colored rocks and a dark bush."
+*   "In the upper right corner, a portion of another light fixture is visible."
+*   "The scene is dark, indicating nighttime, with the primary illumination coming from the garden light."
+**Final Polish:** Combine into a cohesive paragraph. Ensure spatial relationships are clear (left, right, next to). Check for accuracy (don't guess the text on the meter, just say "embossed text").
+*Self-Correction during drafting:* I initially thought the light was casting shadows *of* something, but looking closer, the light fixture itself seems to have a lens that projects the pattern. Wait, looking very closely at the light, it's a standard solar light. The pattern on the ground looks like the light is shining through a textured lens or perhaps reflecting off a textured surface? No, looking at the rays, they look like the light is shining *through* a textured lens or the ground is textured. Actually, looking at the light fixture, it's a standard solar stake light. The pattern on the ground looks like the light is shining through a specific lens or perhaps the light is reflecting off a textured surface nearby? No, the rays are distinct. It looks like the light is projecting a pattern. Let's describe it as a "radial pattern of light and shadow."
+Let's look at the utility cover again. It says "METER" clearly. There are stars around it.
+Let's look at the curb. It's a low concrete retaining wall or curb.
+Let's look at the rocks. They are white/grey, rough stones.
+Okay, ready to write.
+A small, black solar-powered garden light stands in a patch of dark soil next to a grey concrete walkway, casting a distinct, radial pattern of bright, starburst-like rays across the pavement. The light fixture features a black dome top and a thin metal stake. To the right of the light, embedded in the dirt, is a round, bronze-colored utility meter cover with embossed text and stars visible on its surface. A low concrete curb runs diagonally from the bottom center toward the right, separating the walkway from the garden bed. On the far right edge, rough, light-colored rocks and a dark, leafy bush are visible. In the upper right corner,</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -2732,7 +2826,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -2747,7 +2841,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -2772,32 +2866,28 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.8102</t>
+          <t>0.8154</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.8208</t>
+          <t>0.8746</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.7257</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0.2971</t>
-        </is>
-      </c>
+          <t>0.7196</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.1264</t>
+          <t>0.1175</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.1862</t>
+          <t>0.1866</t>
         </is>
       </c>
     </row>
@@ -2825,25 +2915,27 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>Thinking: The user wants a detailed description of the image.
-1.  **Identify the main subject:** A Monarch butterfly resting on a small purple flower.
-2.  **Identify the secondary subject:** A human hand reaching out to touch or support the butterfly.
-3.  **Describe the setting/background:** A dense patch of green vegetation, likely a garden or roadside. There's a paved surface (road or sidewalk) visible in the upper right.
-4.  **Detail the butterfly:** Orange wings with black veins and white spots along the edges. It's perched on a cluster of tiny purple flowers.
-5.  **Detail the hand:** A right hand, light-skinned, fingers extended, gently touching the butterfly's wing or the flower it's on. The arm extends from the right edge.
-6.  **Detail the vegetation:** Various green plants. Some have long, slender leaves (looks like mint or similar herbaceous plants). Others have broader leaves. There are scattered purple flowers and a few yellow flowers in the lower right.
-7.  **Lighting:** Bright, natural sunlight. Shadows are cast on the pavement and the plants, suggesting a sunny day.
-8.  **Spatial relationships:** The hand is on the right, reaching left towards the center. The butterfly is central. The plants fill the left and bottom. The pavement is top right.
+1.  **Identify the main subject:** A Monarch butterfly is the central focus. It's resting on a small cluster of purple flowers.
+2.  **Identify the secondary subject:** A human hand is reaching in from the right side, gently touching or hovering near the butterfly.
+3.  **Describe the setting/background:** There is a dense patch of green vegetation. It looks like a garden bed or roadside planting. To the right, there's a paved surface, likely a sidewalk or road.
+4.  **Detail the butterfly:** It has orange wings with black veins and white spots along the edges. It's facing slightly left.
+5.  **Detail the hand:** It's a right hand, light-skinned. The fingers are extended, with the index finger and thumb near the butterfly. It looks like a gentle touch.
+6.  **Detail the plants:**
+    *   The butterfly is on a small cluster of tiny purple flowers (looks like Lantana or similar).
+    *   Surrounding it are various green leafy plants. Some have long, slender leaves (maybe mint or similar herbaceous plants). Others have broader leaves.
+    *   There are a few other small purple flowers visible in the background.
+    *   In the bottom right corner, there's a small yellow flower.
+7.  **Lighting:** It's bright, natural sunlight. Shadows are cast on the pavement and the plants, suggesting a sunny day. The light is coming from the upper left, illuminating the butterfly and the hand.
+8.  **Composition:** The hand enters from the right edge. The plants fill the left and center. The pavement is in the upper right background.
 **Drafting the description:**
-A Monarch butterfly with vibrant orange wings patterned with black veins and white spots along the edges rests on a cluster of small purple flowers. A human hand enters from the right side of the frame, fingers extended and gently touching the butterfly's wing or the flower it is perched upon. The hand and arm are light-skinned. The butterfly is surrounded by dense, lush green vegetation consisting of various leafy plants with both broad and slender leaves. Scattered among the greenery are a few other small purple blooms and a single yellow flower in the lower right corner. In the upper right background, a section of gray paved surface, likely a road or sidewalk, is visible with shadows cast across it, indicating bright sunlight. The scene appears to be outdoors in a garden or roadside setting.
-**Refining for flow and constraints:**
-- Start with the main subject (butterfly).
-- Move to the hand.
-- Describe the plants.
-- Describe the background/pavement.
-- Ensure no speculation (e.g., "feeding" - just "resting on").
+A Monarch butterfly with vibrant orange wings patterned with black veins and white spots rests on a small cluster of tiny purple flowers. A human hand enters the frame from the right side, reaching towards the butterfly with fingers gently extended near its wings. The butterfly is positioned amidst a dense bed of green foliage, which includes plants with long, slender leaves and broader, serrated leaves. Scattered throughout the greenery are a few other small purple blooms, and a single yellow flower is visible in the lower right corner. To the right of the vegetation, a gray paved surface, likely a sidewalk or road, runs diagonally into the background, marked by shadows cast by nearby objects. The scene is illuminated by bright, natural sunlight, highlighting the textures of the leaves and the delicate wings of the insect.
+**Refining:**
+*   Make sure to mention the specific interaction (hand near butterfly).
+*   Clarify the plant types generally (greenery, foliage).
+*   Ensure the spatial relationships are clear (hand from right, pavement in background).
 **Final Polish:**
-A Monarch butterfly, characterized by its orange wings with black veins and white marginal spots, rests on a cluster of tiny purple flowers. A human hand reaches in from the right side, fingers extended and gently making contact with the butterfly and the flower. The hand is attached to an arm extending out of the frame. The butterfly is nestled within a dense patch of green vegetation featuring a mix of broad-leafed and slender-leafed plants. Scattered throughout the foliage are additional small purple flowers and a yellow flower visible in the lower right corner. To the upper right, a gray paved surface, likely a road or sidewalk, runs parallel to the vegetation, marked by shadows cast by the bright sunlight.
-A Monarch butterfly, characterized by its orange wings with black veins and white marginal spots, rests on a cluster of tiny purple flowers. A human hand reaches in from the right side, fingers extended and gently making contact with the butterfly and the flower. The hand is attached to an arm extending out of the frame. The butterfly is nestled within a dense patch of green vegetation featuring a mix of broad-leafed and slender-leafed plants. Scattered throughout the foliage are additional small purple flowers and a yellow flower visible in the lower right corner. To the upper right, a gray paved surface, likely a road or sidewalk, runs parallel to the vegetation, marked by shadows cast by the bright sunlight.</t>
+A Monarch butterfly, characterized by its orange wings with black veining and white marginal spots, rests on a small cluster of tiny purple flowers. A human hand reaches into the frame from the right side, with the fingers gently positioned near the butterfly's wings, appearing to offer a light touch or proximity. The insect is situated within a dense patch of green vegetation that fills the left and center of the image, featuring a mix of plants with long, slender leaves and others with broader, textured foliage. Scattered among the greenery are a few other small purple blossoms, and a solitary yellow flower is visible in the bottom right corner. To the right of the garden bed, a gray paved surface, likely a sidewalk or road, extends into the background, where shadows are cast across the ground. The scene is bathed in bright daylight, casting distinct shadows and highlighting the natural colors of the flora and fauna.
+A Monarch butterfly, characterized by its vibrant orange wings patterned with black veins and white spots along the edges, rests on a small cluster of tiny purple flowers. A human hand enters the frame from the right side, reaching toward the butterfly with fingers gently extended near its wings, appearing to hover or make light contact. The insect is situated within a dense patch of green vegetation that dominates the left and center of the image, featuring a mix of plants with long, slender leaves and others with broader, textured foliage. Scattered among the greenery are a few other small purple blossoms, and a solitary yellow flower is visible in the bottom right corner. To the right of the garden bed, a gray paved surface, likely a sidewalk or road, extends diagonally into the background, where shadows are cast across the ground. The scene is bathed in bright daylight, casting distinct shadows and highlighting the natural colors of the flora and fauna.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -2898,32 +2990,32 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.8332</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.5036</t>
+          <t>1.5078</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.6481</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.3291</t>
+          <t>0.3097</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1744</t>
+          <t>0.1445</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>0.2167</t>
         </is>
       </c>
     </row>
@@ -2952,49 +3044,49 @@
         <is>
           <t>Thinking: The user wants a detailed description of the image.
 1.  **Identify the main subject:** It's a black turntable with a vinyl record on it.
-2.  **Identify the secondary subject:** A vinyl record sleeve standing next to the turntable.
+2.  **Identify the secondary subject:** A vinyl record sleeve standing upright next to the turntable.
 3.  **Identify the setting:** A wooden table or stand.
 4.  **Analyze the turntable:**
     *   Brand: "audio-technica" is visible on the front.
     *   Color: Black.
-    *   State: The clear plastic lid is open, hinged at the back.
-    *   Platter: A black vinyl record is spinning (or stationary, looks stationary but ready) on the platter. The label is visible, showing "STYX".
-    *   Tonearm: The tonearm is in the resting position on the right side.
-    *   Controls: Buttons and knobs are visible on the front panel (power, play, stop, etc.).
+    *   Platter: Black vinyl record spinning (or stationary) on the platter.
+    *   Tonearm: Black, positioned over the record.
+    *   Lid: Clear plastic lid is open, hinged at the back.
+    *   Controls: Buttons on the front right (Play, Stop, etc.) and a switch on the front left.
+    *   Text on record label: "STYX" is visible in the center.
 5.  **Analyze the record sleeve:**
-    *   Title: "STYX" in large red letters at the top.
-    *   Subtitle: "KILROY WAS HERE" in smaller white letters below the band name.
-    *   Artwork: Features a stylized, somewhat abstract face with green dotted lines and fiery/orange tones.
+    *   Artist: "STYX" in red/orange letters at the top.
+    *   Album Title: "KILROY WAS HERE" in smaller white letters below the artist name.
+    *   Artwork: Two faces, one seemingly melting or distorted, with green dotted lines connecting them. The background is dark with some fiery/orange tones.
     *   Position: Leaning against the back right of the turntable/stand.
 6.  **Analyze the background/surroundings:**
-    *   Surface: A light brown wooden table with tapered legs.
-    *   Underneath the table: A black bag and an orange object (maybe a brush or tool) are visible on the lower shelf.
-    *   To the right: A metal shelving unit. On the shelf below, a box labeled "MONOPOLY" is partially visible.
-    *   Background: A window with blinds or a screen is behind the turntable. To the right, a glimpse of a room with wooden flooring and a vent.
-7.  **Drafting the description (mental outline):**
-    *   Start with the turntable on the table.
-    *   Mention the open lid.
-    *   Describe the record on the platter.
-    *   Describe the sleeve leaning next to it.
-    *   Mention the brand name.
-    *   Describe the table and what's underneath.
-    *   Mention the shelving unit and the Monopoly box.
-8.  **Refining the description (incorporating specific details):**
-    *   "A black Audio-Technica turntable sits on a light wooden table."
-    *   "The clear plastic lid is propped open."
-    *   "A black vinyl record with a blue and red label featuring the word 'STYX' rests on the platter."
-    *   "To the right, the album cover for 'Kilroy Was Here' by Styx leans against the stand."
-    *   "The cover art shows a stylized face with green dotted lines."
-    *   "Below the table, on a lower shelf, a black bag and an orange object are visible."
-    *   "To the right, a metal shelving unit holds a box of Monopoly."
-    *   "In the background, a window with a dark screen is visible."
-9.  **Final Polish (checking against constraints):**
-    *   No bullet points.
-    *   Fluent prose.
-    *   Accurate details.
-    *Draft:* A black Audio-Technica turntable sits on a light brown wooden table with tapered legs. The turntable's clear plastic lid is hinged open at the back. A black vinyl record with a label displaying the band name "STYX" in red and blue sits on the platter. To the right of the turntable, the album sleeve for "Kilroy Was Here" by Styx leans against the furniture; the cover features a stylized, fiery face with green dotted lines connecting to the band's logo at the top. On the front panel of the turntable, the brand name "audio-technica" is printed in white, along with several control buttons. Beneath the main table surface, a lower shelf holds a black bag and an orange object. To the right, a metal shelving unit is partially visible, with a box of the board game "Monopoly" resting on one of the shelves. In the background, a window covered by a dark screen or blind is visible behind the turntable.
-10. **Final Review:** Looks good. Covers all elements accurately.
-A black Audio-Technica turntable sits on a light brown wooden table with tapered legs. The turntable's clear plastic lid is hinged open at the back, revealing a black vinyl record resting</t>
+    *   Surface: A light brown wooden table.
+    *   Underneath the table: A black bag or cloth, an orange object (maybe a brush or tool), and a box labeled "MONOPOLY" partially visible.
+    *   Behind the turntable: A window with blinds or a screen.
+    *   To the right: A metal shelving unit or rack.
+    *   Floor: Light wood or laminate flooring.
+    *   Vent: A floor vent is visible in the background on the right.
+**Drafting the description:**
+Start with the turntable. It's an Audio-Technica turntable, black, sitting on a wooden table. The clear lid is open. A black vinyl record is on the platter. The label says "STYX".
+Next to it, leaning against the back, is the album cover for "Kilroy Was Here" by Styx. The cover art features two faces with green dotted lines.
+Under the table, there are items like a black bag and a Monopoly box.
+The background shows a window and a metal rack.
+**Refining and expanding:**
+Make it more descriptive.
+"A black Audio-Technica turntable sits on a light brown wooden table."
+"The clear plastic lid is propped open."
+"A black vinyl record rests on the platter, featuring a center label with the text 'STYX'."
+"To the right of the turntable, a vinyl record sleeve stands upright, leaning against the back."
+"The sleeve is for the album 'Kilroy Was Here' by the band Styx, displaying the band's name in red lettering at the top."
+"The album art depicts two stylized faces with green dotted lines connecting them against a dark background with orange highlights."
+"Below the table, partially obscured, are a black bag, an orange object, and the edge of a board game box labeled 'MONOPOLY'."
+"In the background, a window with a dark screen is visible behind the turntable, and to the right, a metal shelving unit and light-colored flooring can be seen."
+**Final Polish:** Combine into a cohesive paragraph. Ensure spatial relationships are clear. Check for accuracy. The record label definitely says STYX. The album cover definitely says STYX and KILROY WAS HERE. The turntable brand is Audio-Technica.
+Let's double check the record label. It looks like the same album cover art on the label itself. Yes, it matches the sleeve.
+Let's check the controls. There are buttons on the right side of the front panel.
+Let's check the items under the table. There's a black cloth/bag, an orange rectangular object (looks like a brush handle or tool), and the corner of a Monopoly box.
+Okay, ready to write.
+A black Audio-Technica turntable sits centrally on a light brown wooden table, its clear plastic lid propped open at the back. A black vinyl record rests on the platter, featuring a center label that displays the band name "STYX" in red text. To the right of the turntable, a vinyl record sleeve stands upright, leaning against the back of the setup. The sleeve is for the album "Kilroy Was Here" by Styx,</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -3009,7 +3101,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -3024,57 +3116,57 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.8094</t>
+          <t>0.8059</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.8509</t>
+          <t>1.0749</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.567</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.2929</t>
+          <t>0.2877</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.1609</t>
+          <t>0.1479</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.2324</t>
+          <t>0.2376</t>
         </is>
       </c>
     </row>
@@ -3101,42 +3193,37 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>The user wants a detailed description of the image.
+          <t>Thinking: The user wants a detailed description of the image.
 1.  **Identify the main subject:** The primary subject is a large, framed photograph mounted on a white wall.
 2.  **Analyze the photograph's content:**
     *   It shows vintage cars, specifically Porsche 356s.
     *   There are two main cars visible in the foreground.
-    *   The car in the immediate foreground is a dark brown or bronze color. It has water droplets on the windshield and hood, suggesting it's wet or raining. The hood is angled towards the viewer.
+    *   The car in the immediate foreground is a dark brown or bronze color. It has water droplets on the hood and windshield, suggesting it's wet or raining. The hood is angled towards the viewer.
     *   Behind it is another car, lighter in color (silver or light grey), also with water droplets. It has "ESSO" and "CITANET" logos on the hood.
     *   The background of the photo shows a fence, palm trees, and other cars in the distance, bathed in warm, golden sunlight (likely sunset or sunrise).
     *   The lighting in the photo creates strong highlights on the wet surfaces.
 3.  **Analyze the setting (the room):**
     *   The photo is mounted on a plain white wall.
     *   Below the photo is a white shelf or ledge.
-    *   On the shelf, there are three small toy cars.
-    *   From left to right: a blue car, a black car, and an orange car. They are positioned roughly centered below the large photo.
+    *   On the shelf, there are three small toy cars lined up.
+    *   From left to right: a blue car, a black car, and an orange car. They are miniature versions of the cars in the photo.
 4.  **Synthesize the description:**
-    *   Start with the large framed photo. Describe the cars (vintage Porsches), the wet surfaces, the logos (Esso), and the background (fence, palm trees, golden light).
-    *   Move to the physical setting: the white wall and the shelf below.
+    *   Start with the large framed photo.
+    *   Describe the cars in the photo (Porsche 356s, wet, golden light).
+    *   Mention the specific details like the "ESSO" logo.
+    *   Describe the background of the photo (fence, trees).
+    *   Move to the foreground/room setting (white wall, shelf).
     *   Describe the toy cars on the shelf (blue, black, orange).
-    *   Mention the frame of the photo (thin, dark wood or metal).
-**Drafting the description:**
-A large, rectangular photograph with a thin, dark frame hangs on a plain white wall. The image within the frame depicts a close-up, low-angle view of vintage sports cars, specifically Porsche 356 models, parked side-by-side. The car in the immediate foreground is a dark, metallic brown or bronze color, its hood and windshield covered in glistening water droplets that catch the warm, golden sunlight. Behind it, a second car, appearing silver or light grey, is partially visible, featuring "ESSO" and "CITANET" decals on its hood. The background of the photograph shows a chain-link fence, palm trees, and other vehicles in the distance, all illuminated by a bright, hazy sun that suggests late afternoon or early morning. Below the framed artwork, a white shelf or ledge runs along the bottom of the wall. Resting on this shelf are three small toy cars arranged in a row: a blue car on the left, a black car in the center, and an orange car on the right. The overall scene appears to be an art installation or a display in a gallery or showroom.
-**Refining based on constraints:**
-- "Describe the main subject(s) first": Yes, the photo.
-- "Then secondary elements": Yes, the shelf and toys.
-- "Background, setting": Yes, white wall, fence in photo.
-- "Lighting": Yes, golden sunlight in photo, ambient light in room.
-- "Notable attributes": Water droplets, logos, toy cars.
-- "Spatial relationships": Foreground car vs background car, shelf below photo.
-- "No speculation": Stick to what is seen.
+    *   Note the spatial relationship (toys are below the photo).
+**Drafting the text:**
+A large, framed photograph hangs on a white wall, depicting a close-up view of vintage Porsche 356 sports cars parked side-by-side. The car in the immediate foreground is a dark, metallic brown, its hood and windshield speckled with water droplets that catch the warm, golden sunlight streaming from the right. Behind it, a second car, appearing silver or light grey, is also wet, featuring visible "ESSO" and "CITANET" decals on its hood. The background of the photograph reveals a chain-link fence, palm trees, and other vehicles in the distance, all bathed in a hazy, sun-drenched atmosphere. Below the framed image, on a white shelf or ledge, sit three miniature toy cars lined up horizontally. From left to right, there is a blue car, a black car, and an orange car, serving as tiny counterparts to the vehicles displayed above. The entire scene is lit by soft, ambient indoor lighting, contrasting with the intense sunlight depicted within the photograph.
+**Refining:**
+*   Make sure to mention the frame color (looks like a thin, light wood or metallic frame).
+*   Clarify the position of the cars in the photo (foreground vs background).
+*   Ensure the description of the toy cars is precise.
 **Final Polish:**
-A large, framed photograph dominates the upper portion of the image, mounted on a stark white wall. The photograph captures a low-angle, close-up view of two vintage Porsche 356 cars parked next to each other. The car in the foreground is a dark, metallic bronze or brown, its hood and windshield speckled with water droplets that reflect the intense, golden sunlight. Behind it, a second car, appearing silver or light grey, is visible with "ESSO" and "CITANET" logos printed on its hood. The background of the photograph reveals a chain-link fence, palm trees, and distant vehicles bathed in a hazy, warm glow. Below the framed image, a white shelf or ledge extends across the bottom of the frame. Resting on this shelf are three miniature toy cars lined up horizontally: a blue car on the left, a black car in the middle, and an orange car on the right. The scene suggests a curated display, possibly in a gallery or showroom, contrasting the large-scale artwork with the small-scale toys.
-Wait, looking closer at the toy cars.
-- Left: Blue.
-- Middle: Black.
-- Right: Orange.
-Yes, that's correct.</t>
+A large, framed photograph mounted on a white wall captures a close-up, low-angle view of vintage Porsche 356 cars parked in a row. The car closest to the viewer is a dark, bronze-colored vehicle, its hood and windshield covered in glistening water droplets that reflect the intense, golden sunlight pouring in from the right side of the frame. Behind it, a second car, appearing silver or light grey, is similarly wet and displays "ESSO" and "CITANET" logos on its hood. The background of the photograph shows a chain-link fence, palm trees, and distant vehicles under a bright, hazy sky. Below the artwork, on a white shelf or ledge, three small toy cars are arranged in a row. From left to right, they are blue, black, and orange, mirroring the scale of the miniature vehicles against the large image above. The frame of the photograph is a thin, light-colored border.
+A large, framed photograph mounted on a white wall captures a close-up, low-angle view of vintage Porsche 356 cars parked in a row. The car closest to the viewer is a dark, bronze-colored vehicle, its hood and windshield covered in glistening water droplets that reflect the intense, golden sunlight pouring in from the right side of the frame. Behind it, a second car, appearing silver or light grey, is similarly wet and displays "ESSO" and "CITANET" logos on its hood. The background of the photograph shows a</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3166,7 +3253,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -3176,14 +3263,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>3.67</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>3.67</t>
-        </is>
-      </c>
       <c r="O5" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -3191,32 +3278,32 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.8234</t>
+          <t>0.8165</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.1944</t>
+          <t>1.3334</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.7121</t>
+          <t>0.6659</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.3449</t>
+          <t>0.3414</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1797</t>
+          <t>0.1899</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.349</t>
+          <t>0.3282</t>
         </is>
       </c>
     </row>
@@ -3249,26 +3336,26 @@
     *   Shape: Irregular, somewhat oval or kidney-shaped.
     *   Color: Painted a vibrant purple/magenta.
     *   Texture: Smooth but with some visible wear or texture from the paint.
-    *   Markings: White paint.
-        *   Text: "You rock!" written in a casual, handwritten font. "You" is on top, "rock!" is below it.
-        *   Decorations: Dotted lines and dashes surrounding the text, creating a sort of border or emphasis. There are also small white dots scattered around.
+    *   Markings:
+        *   Text: "You rock!" written in white, hand-painted letters. "You" is on top, "rock!" is below it.
+        *   Decorations: White dots and short white lines (dashes) surrounding the text, resembling a starburst or sparkle effect.
+        *   Wear: There's a small patch of paint chipping or missing near the top center, revealing the grey stone underneath.
 3.  **Describe the setting/background:**
     *   Surface: Green grass.
-    *   Grass details: Mixed green and some dried/brownish blades. It looks like a lawn.
+    *   Grass details: Mixed green and some dried, brownish blades. It looks like a lawn.
     *   Position: The rock is lying flat on the grass, slightly angled.
 4.  **Lighting:** Natural daylight, casting soft shadows within the grass blades. The rock is well-lit.
 5.  **Composition:** The rock is centered in the frame.
 **Drafting the description:**
-A smooth, irregularly shaped rock painted a vibrant purple rests on a bed of green grass. The rock features white hand-painted lettering that reads "You rock!" with "You" positioned above "rock!" in a casual, slightly uneven script. Surrounding the text are decorative white markings, including dashed lines and scattered dots that frame the message. The grass beneath is a mix of fresh green blades and some dried, brownish tips, filling the entire background. The lighting appears natural and diffuse, highlighting the texture of the painted surface and the individual blades of grass.
-**Refining based on guidelines:**
-- Start with main subject: The purple rock.
-- Secondary elements: The text, the grass.
-- Spatial relationships: Rock on grass.
-- Specifics: "You rock!", white paint, purple base.
-- No speculation: Just describe what is there.
+A smooth, irregularly shaped rock painted a vibrant purple rests on a bed of green grass. The rock features the phrase "You rock!" hand-painted in white capital and lowercase letters, with "You" positioned above "rock!". Surrounding the text are decorative white dots and short dashes, creating a starburst-like pattern. A small patch of paint near the top center has chipped away, revealing the grey stone beneath. The grass surrounding the rock is a mix of fresh green blades and some dried, brownish stalks, filling the entire background. The lighting appears natural and even, highlighting the texture of the painted surface and the individual blades of grass.
+**Refining for constraints:**
+- Single paragraph? Yes.
+- No bullet points? Yes.
+- Specific details? Yes (purple, white text, chipped paint, grass mix).
+- Spatial relationships? Yes (rock on grass, text on rock).
 **Final Polish:**
-A smooth, kidney-shaped rock painted a solid, vibrant purple lies centrally on a patch of mixed green and brown grass. The rock is decorated with white paint, featuring the phrase "You rock!" written in a casual, handwritten font across its face. The word "You" sits above "rock!", and both are surrounded by a border of white dashes and scattered dots. The grass blades surround the rock on all sides, creating a textured, natural background that contrasts with the smooth, painted surface of the stone. The lighting is even, suggesting an outdoor setting during the day.
-A smooth, kidney-shaped rock painted a solid, vibrant purple lies centrally on a patch of mixed green and brown grass. The rock is decorated with white paint, featuring the phrase "You rock!" written in a casual, handwritten font across its face. The word "You" sits above "rock!", and both are surrounded by a border of white dashes and scattered dots. The grass blades surround the rock on all sides, creating a textured, natural background that contrasts with the smooth, painted surface of the stone. The lighting is even, suggesting an outdoor setting during the day.</t>
+A smooth, kidney-shaped rock painted a vibrant shade of purple lies flat on a patch of mixed green and dried grass. The surface of the rock features the phrase "You rock!" hand-painted in white, with the word "You" centered above the larger word "rock!". Surrounding the text are scattered white dots and short dashes that create a decorative, starburst-like border. A small area of paint near the top center has chipped away, revealing the grey stone underneath. The grass blades surround the rock on all sides, with some blades appearing fresh and green while others are dry and brownish, creating a textured natural background.
+A smooth, kidney-shaped rock painted a vibrant shade of purple lies flat on a patch of mixed green and dried grass. The surface of the rock features the phrase "You rock!" hand-painted in white, with the word "You" centered above the larger word "rock!". Surrounding the text are scattered white dots and short dashes that create a decorative, starburst-like border. A small area of paint near the top center has chipped away, revealing the grey stone underneath. The grass blades surround the rock on all sides, with some blades appearing fresh and green while others are dry and brownish, creating a textured natural background.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3283,7 +3370,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -3298,7 +3385,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -3308,27 +3395,27 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.8053</t>
+          <t>0.8112</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.6257</t>
+          <t>1.6577</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -3338,17 +3425,17 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0.2771</t>
+          <t>0.2831</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>0.1088</t>
+          <t>0.1148</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.1501</t>
+          <t>0.1496</t>
         </is>
       </c>
     </row>
@@ -3376,43 +3463,33 @@
       <c r="E7" t="inlineStr">
         <is>
           <t>Thinking: The user wants a detailed description of the image.
-1.  **Identify the main subject:** It's a large, white, sculptural bench with the word "LOVE" painted on it in a colorful, stylized font.
-2.  **Analyze the "LOVE" sculpture:**
-    *   It's a white, cloud-like structure.
-    *   The letters "L", "O", "V", "E" are painted in a rainbow of colors (blue, yellow, red, green).
-    *   The font is bold and slightly rounded.
-    *   The "O" and "V" are intertwined or close together.
-    *   The base of the sculpture is a solid white bench seat.
-    *   Flanking the bench are two large, white, cloud-like mounds on the ground, appearing to support or surround the base.
-3.  **Analyze the background:**
-    *   Behind the sculpture is a large wall or fence.
-    *   The wall is painted with a vibrant, geometric pattern of radiating stripes in red, blue, green, yellow, and pink.
-    *   There is a large black semi-circle shape behind the "LOVE" text.
-    *   On the far left of the wall, there is a small black sign with the number "600" in white.
-4.  **Analyze the setting:**
-    *   The sculpture sits on a wooden deck made of planks running horizontally.
-    *   Above the wall, there is a building with a grey/brown facade and a flat roof.
-    *   The sky is blue with scattered white clouds.
-    *   There are some lights visible on the roofline.
-5.  **Lighting:** Bright daylight, casting shadows under the bench and clouds.
-**Drafting the description:**
-Start with the central object: A white, cloud-shaped bench sculpture featuring the word "LOVE" in colorful, rainbow-striped letters.
-Describe the letters: The letters are bold and stylized, with vertical stripes of blue, yellow, red, and green.
-Describe the base: The sculpture sits on a solid white bench seat, flanked by two large, textured white mounds that resemble clouds or cotton balls on the wooden deck.
-Describe the background wall: Behind the sculpture is a large wall painted with a dynamic, radiating pattern of colorful geometric stripes in red, blue, green, yellow, and pink. A large black semi-circle is painted directly behind the "LOVE" text.
-Mention the number: A small black plaque with the number "600" is visible on the upper left side of the wall.
-Describe the environment: The scene is outdoors on a sunny day with a blue sky and white clouds. The sculpture rests on a wooden deck. Above the wall, a portion of a building with a grey exterior and roof-mounted lights is visible.
-**Refining and combining:**
-A white, sculptural bench sits centrally on a wooden deck, featuring the word "LOVE" painted in large, bold letters with vertical stripes of blue, yellow, red, and green. The letters are set against a backdrop of white, cloud-like shapes that extend down to form a solid bench seat, flanked on the ground by two large, textured white mounds resembling clouds. Behind the sculpture is a large wall painted with a vibrant, geometric pattern of radiating stripes in red, blue, green, yellow, and pink, with a large black semi-circle directly behind the text. A small black sign displaying the number "600" is attached to the upper left corner of the wall. Above the wall, a building with a grey facade and roof-mounted lights is visible against a bright blue sky with scattered white clouds.
-**Final Polish:** Check against constraints.
-- Single detailed caption? Yes.
-- Main subject first? Yes.
-- Specific/precise? Yes.
-- Spatial relationships? Yes (behind, flanked, on top of).
-- No speculation? Yes.
-- No bullet points? Yes.
-Looks good.
-A white, sculptural bench sits centrally on a wooden deck, featuring the word "LOVE" painted in large, bold letters with vertical stripes of blue, yellow, red, and green. The letters are set against a backdrop of white, cloud-like shapes that extend down to form a solid bench seat, flanked on the ground by two large, textured white mounds resembling clouds. Behind the sculpture is a large wall painted with a vibrant, geometric pattern of radiating stripes in red, blue, green, yellow, and pink, with a large black semi-circle directly behind the text. A small black sign displaying the number "600" is attached to the upper left corner of the wall. Above the wall, a building with a grey facade and roof-mounted lights is visible against a bright</t>
+1.  **Identify the main subject:** It's a large, white, cloud-shaped bench or sculpture with the word "love" painted on it in colorful, stylized letters.
+2.  **Analyze the "love" text:** The letters are white with thick, multi-colored outlines (blue, yellow, red, green). The font is somewhat bubbly and rounded.
+3.  **Analyze the bench structure:** It looks like a white, cloud-like base. There are two distinct "cloud" piles on the ground flanking the bench seat. The seat itself is a flat, white rectangular slab.
+4.  **Analyze the background:** Behind the bench is a large wall or fence covered in a mural. The mural features a black circle in the center (behind the "love" text) and radiating colorful stripes (red, blue, green, yellow, pink) creating a sunburst or starburst pattern.
+5.  **Identify specific details:**
+    *   Top left of the wall: A small black sign with the number "600" in white.
+    *   Top of the wall: A grey building structure is visible above the mural.
+    *   Lighting: Bright daylight, casting shadows on the wooden deck.
+    *   Ground: Wooden decking planks running horizontally.
+    *   Sky: Blue sky with white clouds visible at the very top.
+6.  **Spatial relationships:** The bench is in the foreground, centered. The mural is directly behind it. The wooden deck is underneath. The building is above the mural.
+7.  **Drafting the description (mental outline):**
+    *   Start with the central object: The white cloud bench with "love".
+    *   Describe the text details (colors, style).
+    *   Describe the base of the bench (cloud piles).
+    *   Describe the background wall (sunburst pattern, colors).
+    *   Mention the "600" sign.
+    *   Describe the setting (wooden deck, building above, sky).
+8.  **Refining the description (incorporating guidelines):**
+    *   *Subject:* A large, white, cloud-shaped bench sculpture stands centrally on a wooden deck.
+    *   *Text:* The word "love" is painted across the upper portion of the sculpture in a stylized, bubbly font. The letters are white with thick, multi-colored outlines in shades of blue, yellow, red, and green.
+    *   *Base:* Flanking the flat, white bench seat are two large, textured mounds of white material resembling clouds or cotton balls.
+    *   *Background:* Directly behind the sculpture is a large wall or fence covered in a vibrant mural. The mural features a black circle in the center, behind the text, with colorful stripes radiating outward in a sunburst pattern. The stripes include red, blue, green, yellow, and pink.
+    *   *Details:* In the upper left corner of the mural, a small black sign displays the number "600" in white.
+    *   *Setting:* Above the mural, the top of a grey building with dark siding is visible against a bright blue sky with scattered white clouds. The sculpture rests on a wooden deck with planks running horizontally across the frame.
+9.  **Final Polish:** Ensure flow and accuracy. The description looks solid. I will combine these points into a cohesive paragraph.
+A large, white, cloud-shaped bench sculpture stands centrally on a wooden deck, featuring the word "love" painted across its upper section in a stylized, bubbly font. The letters are white with thick, multi-colored outlines in shades of blue, yellow, red, and green. Flanking the flat, white bench seat are two large, textured mounds of white material that resemble fluffy clouds or cotton balls. Directly behind the sculpture is a large wall or fence covered in a vibrant mural. The mural features a black circle in the center, behind the text, with colorful stripes radiating outward in a sunburst pattern. The stripes include red, blue, green, yellow, and pink. In the upper left corner of the mural, a small black sign displays the number "600" in white. Above the mural, the top of a grey building with dark siding is visible against a bright blue sky with scattered white clouds. The sculpture rests on a wooden deck with planks running horizontally across the frame.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3427,7 +3504,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3452,7 +3529,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -3462,37 +3539,37 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.8254</t>
+          <t>0.8253</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.942</t>
+          <t>1.1422</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>0.7276</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.2898</t>
+          <t>0.3054</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1418</t>
+          <t>0.152</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>0.2019</t>
+          <t>0.2149</t>
         </is>
       </c>
     </row>
@@ -3520,31 +3597,33 @@
       <c r="E8" t="inlineStr">
         <is>
           <t>Thinking: The user wants a detailed description of the image.
-1.  **Identify the main subject:** A green insect, specifically a katydid or bush cricket, resting on a tree trunk.
-2.  **Identify secondary elements:** A metal tag nailed into the tree bark.
-3.  **Describe the setting/background:** The bark of a tree, textured with deep grooves and covered in lichen.
-4.  **Analyze details:**
-    *   **Insect:** Bright green, leaf-like body shape (camouflage), long hind legs, six legs visible. It's positioned on the left side of the frame.
-    *   **Tag:** Circular, silver/metallic, nailed in with a nail. The number "2003" is stamped on it. It's on the right side.
-    *   **Tree Bark:** Dark brown/grey, rough, deeply furrowed texture.
-    *   **Lichen:** Patches of white and yellowish-green lichen scattered across the bark.
-    *   **Lighting:** Natural, diffuse light, casting soft shadows in the bark crevices.
-5.  **Drafting the description (mental outline):**
-    *   Start with the insect on the left. Describe its color and shape.
-    *   Move to the tag on the right. Describe its shape, material, and the number.
-    *   Describe the surface they are on (tree bark). Mention the texture and the lichen.
-    *   Combine into a cohesive paragraph.
-6.  **Refining the description (adhering to guidelines):**
-    *   *Subject:* A bright green katydid is perched on the left side of a tree trunk. It has a leaf-like body and long hind legs.
-    *   *Secondary:* To the right of the insect is a round, silver metal tag attached to the bark with a nail. The tag has the number "2003" stamped on it.
-    *   *Background/Setting:* The tree bark is dark brown and grey with a rough, deeply furrowed texture. It is speckled with patches of white and pale yellow lichen.
-    *   *Spatial:* The insect is to the left of the tag. The tag is slightly lower than the insect's center.
-7.  **Final Polish:** "A bright green katydid rests on the rough, dark bark of a tree trunk on the left side of the frame. The insect has a leaf-like body shape and long, slender hind legs. To the right of the insect, a circular silver metal tag is nailed into the wood, displaying the number "2003" stamped in the center. The tree bark is deeply furrowed and textured, scattered with numerous patches of white and pale yellow lichen."
-8.  **Final Check against constraints:** No bullet points? Yes. No speculation? Yes. Specific details? Yes.
-Let's adjust slightly for flow and precision.
-"A bright green katydid is perched on the left side of a tree trunk, its leaf-like body and long hind legs blending with the natural surroundings. To the right of the insect, a round, silver metal tag is affixed to the bark with a nail, featuring the number "2003" stamped clearly on its face. The tree bark is dark brown and grey with a deeply furrowed, rough texture, speckled with scattered patches of white and pale yellow lichen."
-This looks good.
-A bright green katydid is perched on the left side of a tree trunk, its leaf-like body and long hind legs resting against the wood. To the right of the insect, a round, silver metal tag is affixed to the bark with a nail, featuring the number "2003" stamped clearly on its face. The tree bark is dark brown and grey with a deeply furrowed, rough texture, speckled with scattered patches of white and pale yellow lichen.</t>
+1.  **Identify the main subject:** The primary subject is a green insect, specifically a katydid or bush cricket, resting on a tree trunk.
+2.  **Identify secondary elements:** To the right of the insect is a silver metal tag or coin-like object nailed into the tree.
+3.  **Analyze the background/setting:** The background is the rough bark of a tree. It's textured with deep grooves and ridges.
+4.  **Describe details of the insect:**
+    *   Color: Bright green.
+    *   Shape: Elongated, leaf-like body.
+    *   Legs: Long, thin legs, especially the hind legs.
+    *   Position: Facing slightly left, legs spread out.
+    *   Texture: Looks somewhat matte.
+5.  **Describe details of the metal object:**
+    *   Shape: Circular disc.
+    *   Material: Silver/metallic.
+    *   Text: The number "2003" is embossed on the front.
+    *   Attachment: It's attached with a nail or screw head visible at the top.
+6.  **Describe the tree bark:**
+    *   Texture: Rough, deeply furrowed, vertical cracks.
+    *   Color: Dark brown/grey.
+    *   Growth: Patches of white and yellowish lichen are scattered across the bark.
+7.  **Lighting:** Natural, diffuse lighting. No harsh shadows, suggesting an overcast day or shaded area.
+8.  **Composition:** The insect is on the left-center, the tag is on the right-center. The tree trunk runs diagonally from top-left to bottom-right.
+**Drafting the description:**
+A bright green katydid rests on the rough, textured bark of a tree trunk, positioned to the left of a silver metal tag. The insect has a leaf-like body and long, slender legs, with its head oriented towards the left side of the frame. To its right, a circular silver disc is nailed into the wood, featuring the embossed number "2003" in the center. The tree bark is dark brown and grey with deep vertical fissures and is speckled with patches of white and yellowish lichen. The lighting is soft and even, highlighting the details of the insect's exoskeleton and the rough surface of the tree.
+**Refining:**
+Make sure to mention the spatial relationship clearly. The insect is to the left of the tag. The tag is nailed in. The bark texture is prominent.
+**Final Polish:**
+A bright green katydid rests on the rough, deeply furrowed bark of a tree trunk, positioned to the left of a silver metal identification tag. The insect, which has a leaf-like body and long, slender hind legs, is facing slightly left with its legs splayed against the wood. To the right of the insect, a circular silver disc is attached to the tree with a nail, displaying the embossed number "2003" in the center. The tree bark is dark brown and grey, textured with vertical cracks and scattered with patches of white and yellowish lichen. The scene is lit by soft, natural light that emphasizes the contrast between the smooth, green insect and the rugged, lichen-covered surface of the tree.
+A bright green katydid rests on the rough, deeply furrowed bark of a tree trunk, positioned to the left of a silver metal identification tag. The insect, which has a leaf-like body and long, slender hind legs, is facing slightly left with its legs splayed against the wood. To the right of the insect, a circular silver disc is attached to the tree with a nail, displaying the embossed number "2003" in the center. The tree bark is dark brown and grey, textured with vertical cracks and scattered with patches of white and yellowish lichen. The scene is lit by soft, natural light that emphasizes the contrast between the smooth, green insect and the rugged, lichen-covered surface of the tree.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3559,72 +3638,72 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>4.42</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>4.33</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>4.33</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.8193</t>
+          <t>0.821</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.9655</t>
+          <t>2.2328</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0.6238</t>
+          <t>0.6922</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0.3095</t>
+          <t>0.3024</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.1731</t>
+          <t>0.1718</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>0.2299</t>
+          <t>0.2225</t>
         </is>
       </c>
     </row>
@@ -3652,36 +3731,41 @@
       <c r="E9" t="inlineStr">
         <is>
           <t>Thinking: The user wants a detailed description of the image.
-1.  **Identify the main subject:** A large collection of shiny, metallic spheres floating on a body of water.
+1.  **Identify the main subject:** The most prominent feature is a large collection of shiny, metallic spheres floating on the surface of a body of water.
 2.  **Analyze the spheres:**
-    *   They are silver/chrome in color.
-    *   They are highly reflective, showing the surrounding trees and sky.
-    *   They vary slightly in size but generally look uniform.
-    *   They are clustered densely in the background and become more sparse in the foreground.
-    *   There are reflections of the spheres in the water below them.
+    *   **Material:** They look like polished stainless steel or chrome. They are highly reflective.
+    *   **Shape:** Perfect spheres.
+    *   **Size:** They appear to be roughly the same size, perhaps 10-15 cm in diameter.
+    *   **Arrangement:** They are clustered together in the background and middle ground, forming a dense mass. In the foreground, they are more scattered and spaced out.
+    *   **Reflections:** Each sphere reflects the surrounding trees and sky, creating a mosaic of light and dark spots on their surfaces. They also cast reflections on the water below.
 3.  **Analyze the water:**
-    *   It's a greenish, murky color, likely a pond or a slow-moving stream.
-    *   There are small floating debris or leaves scattered on the surface.
-    *   The water is relatively calm, allowing for clear reflections.
+    *   **Color:** Greenish, slightly murky or algae-covered. It has a distinct green hue.
+    *   **Surface:** Relatively calm but with ripples around the spheres. There are small floating debris or leaves scattered on the surface.
+    *   **Reflections:** The water reflects the trees from the bank and the spheres themselves.
 4.  **Analyze the background/setting:**
-    *   It's a wooded area.
-    *   Tall trees with green leaves line the banks.
-    *   The lighting suggests a sunny day, with dappled sunlight filtering through the trees.
-    *   The bank is visible in the distance, covered in vegetation.
-5.  **Spatial relationships:**
-    *   The spheres start densely packed in the upper middle/left and spread out towards the right and foreground.
-    *   Some spheres are further out in the water, isolated from the main cluster.
-    *   The trees are behind the water.
-**Drafting the description:**
-Start with the main subject: A large number of polished, silver spheres are floating on the surface of a green body of water.
-Describe the arrangement: They are densely clustered in the background, forming a long, winding line that stretches across the width of the water, becoming more scattered and sparse as they move into the foreground.
-Describe the spheres' appearance: The spheres are highly reflective, mirroring the surrounding green foliage and sky. Their metallic surfaces gleam in the sunlight.
-Describe the water: The water is a murky green color, speckled with small floating leaves or debris. The spheres cast distinct, inverted reflections on the water's surface.
-Describe the background: The water is bordered by a dense forest with tall trees and lush green undergrowth. Sunlight filters through the canopy, creating dappled light on the scene.
-Refine for flow and detail: Ensure the distinction between the dense cluster and the scattered foreground spheres is clear. Mention the specific reflections.
-**Final Polish:**
-A large collection of polished, silver spheres floats on the surface of a calm, green body of water, likely a pond or slow-moving stream. The spheres are densely packed in the background, forming a long, meandering cluster that stretches across the water's width, while becoming increasingly sparse and scattered as they extend into the foreground. Each sphere is highly reflective, mirroring the surrounding trees and sky, and casts a clear, inverted reflection on the water below. The water itself is a murky green, speckled with small floating leaves and debris. The scene is set in a wooded area, with tall trees and dense green foliage lining the banks in the background, illuminated by bright, dappled sunlight filtering through the canopy.
-A large collection of polished, silver spheres floats on the surface of a calm, green body of water, likely a pond or slow-moving stream. The spheres are densely packed in the background, forming a long, meandering cluster that stretches across the water's width, while becoming increasingly sparse and scattered as they extend into the foreground. Each sphere is highly reflective, mirroring the surrounding trees and sky, and casts a clear, inverted reflection on the water below. The water itself is a murky green, speckled with small floating leaves and debris. The scene is set in a wooded area, with tall trees and dense green foliage lining the banks in the background, illuminated by bright, dappled sunlight filtering through the canopy.</t>
+    *   **Location:** A wooded area. It looks like a pond or a slow-moving stream in a forest.
+    *   **Vegetation:** Dense green trees and bushes line the far bank. The foliage is lush, suggesting summer.
+    *   **Trees:** Several tall tree trunks are visible on the left side.
+5.  **Lighting:**
+    *   **Source:** Natural daylight. It seems sunny, given the bright highlights on the metal spheres and the dappled light in the trees.
+    *   **Shadows:** Shadows are cast by the trees onto the bank and water.
+**Drafting the description (mental outline):**
+*   Start with the spheres. Hundreds of them. Floating.
+*   Describe their appearance: silver, reflective, chrome-like.
+*   Describe the water: green, calm, with some debris.
+*   Describe the background: forest, trees, greenery.
+*   Mention the spatial arrangement: dense cluster in back, scattered in front.
+**Refining the description:**
+*   "A large number of polished metal spheres float on a green body of water." -&gt; "Hundreds of highly reflective, silver-colored spheres float on the surface of a calm, green body of water."
+*   "They are in a forest." -&gt; "The setting is a wooded area with dense green foliage and tall trees lining the far bank."
+*   "The spheres are shiny." -&gt; "The spheres are made of a polished material, likely stainless steel, which mirrors the surrounding trees and sky."
+*   "There are more spheres in the back." -&gt; "In the background, the spheres are densely packed together, creating a solid wall of metal. In the foreground, they are more loosely scattered."
+*   "The water is green." -&gt; "The water has a distinct greenish tint, possibly due to algae or reflection of the surrounding vegetation, and is speckled with small floating leaves or debris."
+**Final Polish:** Combine these observations into a cohesive paragraph. Ensure no speculation (e.g., "it's an art installation" - though likely, I should stick to describing what is seen).
+*   *Self-Correction during drafting:* I shouldn't say "it's a pond" definitively, just "body of water." I shouldn't guess the exact number, just "hundreds" or "large collection."
+**Final Output Generation:** (Matches the drafted points)
+"A large collection of highly reflective, silver-colored spheres floats on the surface of a calm, green body of water. The spheres, which appear to be made of polished stainless steel or chrome, are arranged in a dense cluster in the background and middle distance, gradually becoming more scattered and spaced out in the foreground. Each sphere acts as a mirror, capturing reflections of the surrounding trees and sky, while also casting a distinct, inverted reflection onto the water's surface below. The water itself is a murky green hue, speckled with small floating leaves and organic debris. The setting is a lush, wooded area, with a dense line of green trees and bushes forming the far bank. Several tall, slender tree trunks are visible on the left side, rising from the water's edge into the canopy. The lighting suggests a bright, sunny day, illuminating the metallic surfaces and highlighting the vibrant greenery of the forest."
+A large collection of highly reflective, silver-colored spheres floats on the surface of a calm, green body of water. The spheres, which appear to be made of polished stainless steel or chrome, are arranged in a dense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -3696,7 +3780,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3711,22 +3795,22 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>4.67</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>4.33</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3736,32 +3820,32 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.8072</t>
+          <t>0.8046</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.852</t>
+          <t>0.694</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.6746</t>
+          <t>0.6449</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.2621</t>
+          <t>0.2511</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>0.1111</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.1642</t>
+          <t>0.1473</t>
         </is>
       </c>
     </row>
@@ -3788,36 +3872,35 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Thinking: The user wants a detailed description of the image.
-1.  **Identify the main subjects:** There are two large ships floating on the water.
-2.  **Analyze the setting:** The background is a vast expanse of blue water, likely the ocean or a large sea. The water is relatively calm with small ripples.
-3.  **Analyze the first ship (top right):**
+          <t>Thinking: The user wants a detailed description of the provided image.
+1.  **Identify the main subjects:** There are two large ships floating on a vast body of water.
+2.  **Analyze the setting:** The water is a uniform, deep blue, suggesting a large ocean or sea. The view is from a high angle, likely aerial (drone or plane).
+3.  **Describe the first ship (top right):**
     *   Position: Upper right quadrant.
-    *   Type: Looks like a container ship or a large cargo vessel.
-    *   Color: The hull is dark, possibly black or dark grey. The bow (front) has a distinct reddish-pink anti-fouling paint.
-    *   Details: The deck is visible, appearing somewhat cluttered with containers or cargo. There's a white structure, likely a bridge or superstructure, near the stern (rear).
-    *   Orientation: Angled slightly towards the left.
-4.  **Analyze the second ship (bottom left):**
+    *   Type: Looks like a container ship or bulk carrier.
+    *   Color: The hull is dark, possibly black or dark grey. The bow (front) has a distinct reddish-pink stripe or paint.
+    *   Details: It's carrying a load of containers or cargo stacked high. The top of the cargo is visible.
+4.  **Describe the second ship (bottom left):**
     *   Position: Lower left quadrant.
-    *   Type: Also looks like a container ship or cargo vessel.
-    *   Color: The hull is grey/white. The bow is white.
-    *   Details: Similar to the first ship, it has a deck loaded with containers. There are white structures on the deck, likely cranes or superstructures.
-    *   Orientation: Angled slightly towards the right, almost parallel to the first ship but facing the opposite direction or slightly angled.
-5.  **Analyze spatial relationships:** The ships are separated by a significant distance. They are roughly diagonal from each other.
-6.  **Lighting/Atmosphere:** The lighting is bright, suggesting daytime. The image has a slightly hazy or washed-out quality, typical of a photo taken from a distance (like a plane or high vantage point). The blue of the water dominates the frame.
+    *   Type: Similar to the first, likely a container ship.
+    *   Color: The hull is grey/white.
+    *   Details: It is also carrying stacked containers. The bridge/superstructure is visible at the rear (right side of the ship from this angle).
+5.  **Describe the spatial relationship:** The ships are separated by a significant distance, floating parallel to each other but angled slightly differently. They are isolated in the open water.
+6.  **Lighting/Atmosphere:** The lighting is diffuse, suggesting an overcast day or haze. The colors are somewhat muted due to the distance and atmospheric conditions. The water is calm with very small ripples.
 7.  **Drafting the description:**
-    *   Start with the overall scene: Two large ships on blue water.
-    *   Describe the top ship: Located in the upper right, dark hull, pink bow, cargo on deck.
-    *   Describe the bottom ship: Located in the lower left, lighter hull, white bow, cargo on deck.
-    *   Describe the water: Deep blue, calm, fills the rest of the frame.
-    *   Refine details: Mention the perspective (aerial/high angle). Note the lack of other objects.
-Let's refine the description of the ships.
-- Top ship: Dark hull, reddish-pink bow. Deck is filled with what looks like containers.
-- Bottom ship: Lighter hull (grey/white), white bow. Deck has containers.
-- Water: Uniform blue, slight texture of waves.
-Final Polish:
-An aerial, high-angle shot captures two large cargo ships navigating a vast expanse of deep blue water. In the upper right quadrant, a large vessel with a dark hull and a distinct reddish-pink bow floats diagonally, its deck crowded with stacked cargo containers and topped by a white superstructure. Further down and to the left, a second ship is visible, oriented somewhat parallel but facing the opposite direction. This vessel features a lighter, greyish-white hull and a white bow, also carrying a load of containers on its deck. The surrounding water is a uniform, calm blue, filling the majority of the frame and emphasizing the isolation of the vessels. The lighting is bright and diffuse, casting soft shadows beneath the ships.
-An aerial, high-angle shot captures two large cargo ships navigating a vast expanse of deep blue water. In the upper right quadrant, a large vessel with a dark hull and a distinct reddish-pink bow floats diagonally, its deck crowded with stacked cargo containers and topped by a white superstructure. Further down and to the left, a second ship is visible, oriented somewhat parallel but facing the opposite direction. This vessel features a lighter, greyish-white hull and a white bow, also carrying a load of containers on its deck. The surrounding water is a uniform, calm blue, filling the majority of the frame and emphasizing the isolation of the vessels. The lighting is bright and diffuse, casting soft shadows beneath the ships.</t>
+    *   Start with the overall scene: Two large cargo ships on blue water.
+    *   Detail the top ship: Located in the upper right, dark hull, pinkish bow, stacked cargo.
+    *   Detail the bottom ship: Located in the lower left, grey hull, stacked cargo, superstructure visible.
+    *   Describe the water: Deep blue, calm, expansive.
+    *   Mention the perspective: High-angle shot.
+Refining the description for flow and accuracy:
+- "Two large cargo vessels are visible floating on a vast expanse of deep blue water."
+- "The vessel in the upper right quadrant appears to be a container ship with a dark hull and a distinct reddish-pink stripe along its bow. It is heavily laden with stacked cargo containers."
+- "The second vessel is positioned in the lower left quadrant. It has a grey hull and is also carrying a load of stacked containers. Its superstructure is visible towards the rear."
+- "The water is relatively calm with a uniform blue hue, and the perspective suggests an aerial view looking down upon the ships."
+Final Polish: Ensure no speculation about *why* they are there or *where* exactly. Just what is seen.
+Let's combine these observations into the final output.
+Two large cargo vessels are visible floating on a vast expanse of deep blue water, captured from a high-angle aerial perspective. The ship in the upper right quadrant features a dark hull with a distinct reddish-pink stripe along its bow and is heavily laden with stacked cargo containers. The second vessel is positioned in the lower left quadrant; it has a grey hull and is similarly loaded with stacked containers, with its white superstructure visible near the stern. The water is calm and uniform in color, stretching out to the edges of the frame with no land or other objects in sight. The lighting is diffuse, suggesting an overcast day or atmospheric haze that softens the details of the ships.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3832,72 +3915,72 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>4.08</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>4.67</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>3.67</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>4.67</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>3.67</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>3.33</t>
-        </is>
-      </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.8089</t>
+          <t>0.8069</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.897</t>
+          <t>0.8303</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.689</t>
+          <t>0.7594</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0.2944</t>
+          <t>0.3273</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0.1344</t>
+          <t>0.1548</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>0.2085</t>
+          <t>0.2384</t>
         </is>
       </c>
     </row>
@@ -3931,11 +4014,11 @@
     *   Model: 320E.
     *   Serial/ID number: TF100332.
     *   Configuration: It has a grapple attachment (claw) instead of a standard bucket.
-    *   Tracks: Heavy-duty rubber or steel tracks (looks like rubber with metal cleats, typical for CAT).
+    *   Tracks: Heavy-duty rubber or steel tracks (looks like rubber with metal lugs, typical for CAT).
     *   Cab: Glass cab visible.
     *   Boom/Arm: Extended, reaching towards the right side.
 3.  **Identify the setting/background:**
-    *   Time of day: Nighttime or very late dusk (dark blue sky).
+    *   Time of day: Night or very late dusk (dark blue sky).
     *   Location: Looks like a residential or semi-rural area. There's a curb and grass in the foreground.
     *   Ground: Dirt/mulch area where the excavator is parked.
     *   Background elements: Trees, a chain-link fence, a car visible through the fence, utility poles.
@@ -3945,23 +4028,19 @@
     *   Grapple is on the right.
     *   Curb is at the bottom.
     *   Fence is in the background right.
-**Drafting the description:**
-Start with the excavator. It's a yellow Caterpillar 320E excavator. It has the ID "TF100332" on the side. It's equipped with a large, multi-pronged grapple attachment. The arm is extended.
-Describe the tracks. They are resting on a patch of dirt and mulch.
-Describe the foreground. There is a concrete curb and green grass.
-Describe the background. Dark blue sky. Trees. A chain-link fence. A car is visible behind the fence.
-Mention lighting. The machine is lit up, likely by work lights, against the dark sky.
-**Refining the description for flow and detail:**
-A large yellow Caterpillar 320E excavator dominates the frame, positioned on a patch of disturbed earth and mulch. The machine is angled slightly towards the right, with its long hydraulic arm extended and a heavy-duty, multi-pronged grapple attachment resting on the ground. The side of the excavator's body displays the "CAT" logo, the model number "320E," and the identification code "TF100332." The tracks are caked with dirt. In the immediate foreground, a concrete curb separates the work area from a strip of green grass. Behind the excavator, the background features a dark blue night sky, silhouetted trees, and a chain-link fence. Through the fence, a silver car is partially visible. Utility poles and wires are faintly visible in the distance against the twilight sky. The scene is illuminated by artificial light, casting shadows from the machinery onto the ground.
+**Drafting the description (mental outline):**
+Start with the excavator. It's a yellow CAT 320E. It has a grapple. It's parked on dirt next to grass. The sky is dark blue. In the background, there's a fence and a car.
+**Refining and expanding (adding detail):**
+A large yellow Caterpillar (CAT) 320E excavator dominates the foreground, positioned on a patch of disturbed earth and mulch. The machine is angled slightly towards the right, with its tracks resting on the ground. The side of the engine housing displays the text "TF100332" and the model number "320E" along with the CAT logo. The excavator's arm extends upward and to the right, ending in a heavy-duty grapple attachment with four curved tines, resting near the ground.
+The foreground features a concrete curb separating the dirt work area from a strip of green grass and a paved road surface at the very bottom. Behind the excavator, the background reveals a dark blue night sky. To the right, a chain-link fence runs horizontally, behind which a silver car is parked. Tall trees with dark foliage frame the top and left sides of the image. Utility poles are faintly visible in the distance against the twilight sky. The scene is illuminated by artificial light, likely from a streetlamp or work light, casting shadows from the machinery onto the ground.
 **Final Polish:** Check against constraints.
-- Single detailed caption? Yes.
-- Main subject first? Yes.
-- Specific/precise? Yes (CAT 320E, TF100332, grapple).
-- Spatial relationships? Yes (foreground curb, background fence).
+- Single paragraph? Yes.
+- No bullet points? Yes.
+- Specific details? Yes (model, serial, grapple, fence, car).
 - No speculation? Yes.
-- No bullet points? Yes.
-Looks good.
-A large yellow Caterpillar 320E excavator dominates the scene, positioned on a patch of disturbed earth and mulch under a dark blue night sky. The heavy machinery is angled slightly to the right, with its long hydraulic boom and arm extended, ending in a large, multi-pronged grapple attachment that rests on the ground. The side of the excavator's body features the "CAT" logo, the model designation "320E," and the identification code "TF100332" in black lettering. The machine sits on heavy-duty tracks that show signs of use. In the immediate foreground, a concrete curb runs horizontally, separating the dirt work area from a strip of green grass. Behind the excavator, the background includes silhouetted trees, a chain-link fence, and a silver car visible through the fence mesh. Utility poles and wires are faintly visible in the distance against the twilight sky, and the scene is illuminated by artificial light, casting distinct shadows from the equipment.</t>
+Let's combine into the final output.
+A large yellow Caterpillar (CAT) 320E excavator dominates the foreground, positioned on a patch of disturbed earth and mulch. The machine is angled slightly towards the right, with its heavy-duty tracks resting on the ground. The side of the engine housing displays the identification number "TF100332" and the model designation "320E" alongside the black and yellow CAT logo. The excavator's boom and arm extend upward and to the right, ending in a heavy-duty grapple attachment with four curved metal tines that rest near the ground.
+In the immediate foreground, a concrete curb separates the dirt work area from a strip of green grass and a paved road surface at the very bottom. Behind the excavator, the background reveals a deep blue night sky. To the right, a chain-link fence runs horizontally, behind which a silver car is parked in a driveway or parking area. Tall trees with dark foliage frame the top and left sides of the image, and utility poles are faintly visible in the distance against the twilight sky. The scene is illuminated by artificial light, casting distinct shadows from the machinery onto the ground.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3976,7 +4055,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4001,12 +4080,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4016,12 +4095,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.8063</t>
+          <t>0.8084</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.0363</t>
+          <t>0.9957</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -4031,17 +4110,17 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>0.3288</t>
+          <t>0.306</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>0.1605</t>
+          <t>0.1583</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>0.2764</t>
         </is>
       </c>
     </row>
@@ -4096,13 +4175,13 @@
     *   Trim: White baseboard molding along the bottom of the wall.
     *   Wall color: A pale yellow or cream color on the sides of the door frame.
 7.  **Lighting:** Even, indoor lighting. Shadows are cast slightly to the right of the rackets on the door.
-8.  **Synthesize into a cohesive paragraph:** Start with the rackets, move to their specific details, then describe the background elements.
+8.  **Synthesize into a cohesive paragraph:** Start with the rackets, move left to right, then describe the background elements.
 *Drafting the description:*
-Three tennis rackets stand upright in a row, leaning against a white paneled door. The racket on the far left features a black frame with blue accents along the throat and the outer rim of the head. The middle and right rackets are nearly identical, featuring black frames with bright neon yellow accents on the throat and rim. All three rackets have black handles wrapped in grip tape and standard black stringing. They are positioned on a light-colored wooden floor with visible grain. Behind them is a white door with vertical molding, flanked by walls painted a pale yellow or cream color. White baseboard trim runs along the bottom of the wall where it meets the floor. The lighting casts soft shadows of the rackets onto the door behind them.
-*Refining:* Ensure specific details like the brand name "Babolat" are mentioned if clearly visible (it is, though slightly blurry, the shape and color match). The prompt asks for factual description. I see "Babolat" written on the throat of the left one in blue and the middle/right ones in yellow.
+Three tennis rackets stand upright in a row, leaning against a white paneled door. The rackets are arranged from left to right. The leftmost racket features a black frame with blue accents along the throat and the outer rim of the head; the brand name "Babolat" is printed in blue on the throat. The middle racket has a black frame with bright neon yellow accents on the throat and rim, with "Babolat" printed in matching neon yellow. The rightmost racket is identical in design to the middle one, featuring a black frame with neon yellow accents and the "Babolat" logo. All three rackets have black overgrips on their handles and standard black stringing. They rest on a light-colored wooden floor with visible grain. Behind them is a white door with vertical molding, flanked by walls painted a pale yellow or cream color. White baseboard trim runs along the bottom of the wall where it meets the floor. Shadows are cast by the rackets onto the door behind them.
+*Refining:* Ensure no hallucinations. The text "Babolat" is clearly visible. The colors are accurate. The spatial relationships are clear.
 *Final Polish:*
-Three tennis rackets stand upright in a horizontal row, leaning against a white paneled door. The racket on the far left has a black frame with blue accents on the throat and the outer rim of the head, with the brand name "Babolat" visible in blue lettering. The middle and right rackets are similar in design but feature bright neon yellow accents on the throat and rim, with the brand name "Babolat" visible in matching yellow lettering. All three rackets have black handles wrapped in grip tape and are strung with black strings. They rest on a light-colored wooden floor with a visible wood grain pattern. The background consists of a white door with vertical paneling, flanked by walls painted a pale yellow or cream color. White baseboard molding runs along the bottom of the wall, separating it from the floor. Soft shadows are cast by the rackets onto the door behind them.
-Three tennis rackets stand upright in a horizontal row, leaning against a white paneled door. The racket on the far left has a black frame with blue accents on the throat and the outer rim of the head, with the brand name "Babolat" visible in blue lettering. The middle and right rackets are similar in design but feature bright neon yellow accents on the throat and rim, with the brand name "Babolat" visible in matching yellow lettering. All three rackets have black handles wrapped in grip tape and are strung with black strings. They rest on a light-colored wooden floor with a visible wood grain pattern. The background consists of a white door with vertical paneling, flanked by walls painted a pale yellow or cream color. White baseboard molding runs along the bottom of the wall, separating it from the floor. Soft shadows</t>
+Three tennis rackets stand upright in a horizontal row, leaning against a white paneled door. From left to right, the first racket has a black frame with blue accents on the throat and the outer rim of the head, featuring the brand name "Babolat" in blue lettering. The middle and rightmost rackets share a similar design, featuring black frames with bright neon yellow accents on the throat and rim, with the "Babolat" logo printed in neon yellow. All three rackets have black handles wrapped in grip tape and standard black stringing. They are positioned on a light-colored wooden floor with a visible wood grain pattern. The background consists of a white door with vertical paneling, set against walls painted a pale yellow or cream color. White baseboard molding runs along the bottom of the wall, separating it from the floor. Soft shadows are cast by the rackets onto the door behind them.
+Three tennis rackets stand upright in a horizontal row, leaning against a white paneled door. From left to right, the first racket has a black frame with blue accents on the throat and the outer rim of the head, featuring the brand name "Babolat" in blue lettering. The middle and rightmost rackets share a similar design, featuring black frames with bright neon yellow accents on the throat and rim, with the "Babolat" logo printed in neon yellow. All three rackets have black handles wrapped in grip tape and standard black stringing. They are positioned on a light-colored wooden floor with a visible wood grain pattern. The background consists of a white door with vertical paneling, set against walls painted a pale yellow or cream color</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -4117,7 +4196,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -4132,37 +4211,37 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.8122</t>
+          <t>0.8119</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1.507</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -4172,17 +4251,17 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.3209</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>0.1684</t>
+          <t>0.157</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0.2821</t>
+          <t>0.2818</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4313,7 @@
 *   *Sculpture:* "A large, stylized sculpture of a cream-colored cow stands centrally..."
 *   *Grass:* "...positioned behind a bright lime-green rectangular block featuring jagged, grass-like spikes along its top edge."
 *   *Pedestal:* "The entire assembly rests on a long, white rectangular plinth."
-*   *Background Art 1:* "On the wall behind the sculpture hangs a large, black-and-white artwork that appears to be a collage or complex drawing featuring various figures and abstract shapes."
+*   *Background Art 1:* "On the wall behind the sculpture hangs a large, black-and-white artwork that appears to be a complex collage or drawing featuring various figures and abstract shapes."
 *   *Background Art 2:* "To the right, further back on the adjacent wall, is a smaller, framed painting with a sepia-toned or muted color palette depicting a scene with figures."
 *   *Background Art 3:* "On the far right edge, a portion of another artwork is visible, showing a hand holding a cigarette near a white, sculptural form."
 *   *Setting:* "The room has light wood flooring and neutral beige walls. A doorway is visible on the left. Track lighting is mounted on the ceiling."
@@ -4256,7 +4335,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -4276,17 +4355,17 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -4301,7 +4380,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>0.5816</t>
+          <t>0.5818</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -4350,46 +4429,54 @@
       <c r="E14" t="inlineStr">
         <is>
           <t>Thinking: The user wants a detailed description of the image.
-1.  **Main Subject:** A concrete bridge spanning a body of water.
-2.  **Bridge Details:**
-    *   Material: Grey concrete.
+1.  **Identify the main subject:** The central focus is a concrete bridge spanning a body of water.
+2.  **Analyze the bridge:**
+    *   Material: Concrete, light gray.
     *   Structure: Single arch.
-    *   Features: Vertical fluting or grooves on the side walls (piers/abutments). A decorative element in the center of the arch (looks like three vertical columns or fluted pilasters).
-    *   Top: Flat roadway surface.
-    *   Left side: A white sign with "20" visible (likely a speed limit sign).
-3.  **Water:**
-    *   Color: Murky, greenish-brown.
+    *   Details: There's a decorative element in the center of the arch (vertical fluting or grooves). There are vertical grooves on the side walls (piers/abutments).
+    *   Top: A flat roadway surface.
+    *   Left side: A white sign with "20" visible on it.
+3.  **Analyze the water:**
+    *   Color: Murky, greenish-brown (olive drab).
     *   Surface: Rippled, reflecting the sky and bridge.
     *   Under the bridge: Dark shadow, indicating depth or lack of light.
-4.  **Background/Setting:**
+4.  **Analyze the background/setting:**
     *   Sky: Bright blue with scattered white clouds.
     *   Vegetation: Several palm trees (likely palmettos) on the left and right banks. Green leafy trees further back.
-    *   Distant buildings: White, multi-story buildings visible in the distance behind the trees.
-5.  **Lighting:** Bright daylight, casting shadows under the bridge and on the right side of the bridge structure.
+    *   Distant buildings: White, multi-story buildings are visible in the distance behind the trees.
+5.  **Analyze lighting:**
+    *   Bright daylight. Shadows are cast under the bridge and by the trees onto the bridge deck.
+6.  **Spatial relationships:**
+    *   Bridge is in the foreground/mid-ground.
+    *   Water is below the bridge.
+    *   Trees frame the bridge on both sides.
+    *   Buildings are in the far background.
 **Drafting the description:**
-Start with the bridge. It's a concrete arch bridge.
-Describe the water below. It's greenish and calm but rippled.
-Describe the surroundings. Palm trees on both sides. Blue sky above.
-Mention the sign on the left.
-Mention the distant buildings.
+Start with the bridge. It's a concrete arch bridge. Mention the decorative center.
+Move to the water. It's greenish and calm.
+Describe the surroundings. Palm trees on the left and right.
+Mention the background. Blue sky, clouds, distant white buildings.
+Note the sign on the left.
 **Refining the description:**
-"A concrete arch bridge spans a murky, greenish-brown body of water under a bright blue sky with scattered white clouds." -&gt; Good start.
-"The bridge features a single, rounded arch with vertical fluting on the side walls and a decorative, column-like element centered on the arch's apex." -&gt; Specific details.
-"To the left, a white rectangular sign displays the number '20'." -&gt; Specific detail.
-"Behind the bridge, lush greenery includes several palm trees on the left bank and a large tree overhanging the right side." -&gt; Vegetation.
-"In the distance, white multi-story buildings are visible through the trees." -&gt; Background.
-"The water reflects the blue sky in the center of the arch but is dark and shadowed beneath the bridge structure." -&gt; Water details.
+"A concrete arch bridge spans a murky, greenish-brown body of water under a bright blue sky." -&gt; Good start.
+"The bridge features a single, rounded arch with a decorative, fluted concrete element centered on the arch's apex." -&gt; Specific detail.
+"Vertical grooves run down the side walls of the bridge structure." -&gt; Architectural detail.
+"To the left, a white rectangular sign displays the number '20'." -&gt; Specific text.
+"Flanking the bridge are clusters of palm trees and other green foliage." -&gt; Vegetation.
+"In the distance, beyond the tree line, white multi-story buildings are visible." -&gt; Background context.
+"The water reflects the blue sky and the underside of the bridge, which is cast in shadow." -&gt; Lighting/Reflection.
 **Final Polish:** Combine into a cohesive paragraph.
-"A concrete arch bridge spans a murky, greenish-brown body of water under a bright blue sky scattered with white clouds. The bridge is constructed of grey concrete and features a single rounded arch with vertical fluting on the side walls and a decorative, column-like element centered on the arch's apex. To the far left, a white rectangular sign displays the number '20'. Behind the bridge, lush greenery includes several palm trees on the left bank and a large tree with dense foliage overhanging the right side. In the distance, white multi-story buildings are visible through the trees. The water reflects the blue sky in the center of the arch but is dark and shadowed beneath the bridge structure, with gentle ripples visible on the surface."
+"A light gray concrete arch bridge spans a body of murky, olive-green water under a bright blue sky scattered with white clouds. The bridge features a single, rounded arch with a decorative, vertically fluted concrete element centered on the arch's apex, and vertical grooves run down the side walls. To the far left, a white rectangular sign with the number '20' is visible. Flanking the bridge on both sides are clusters of palm trees and dense green foliage. In the background, beyond the tree line, white multi-story buildings can be seen. The water beneath the bridge is dark and shadowed, while the surface outside the arch reflects the sky and the bridge structure."
 Check against constraints:
 - Single detailed factual caption? Yes.
-- Main subject first? Yes.
-- Specific/precise? Yes.
-- Spatial relationships? Yes (left, right, behind, beneath).
+- Main subject first? Yes (bridge).
+- Secondary elements? Yes (water, trees, buildings).
+- Specific/Precise? Yes (concrete, fluted, olive-green, number 20).
+- Spatial relationships? Yes (spans, flanking, background).
 - No speculation? Yes.
 - No bullet points? Yes.
 Looks good.
-A concrete arch bridge spans a murky, greenish-brown body of water under a bright blue sky scattered with white clouds. The bridge is constructed of grey concrete and features a single rounded arch with vertical fluting on the side walls and a decorative, column-like element centered on the arch's apex. To the far left, a white rectangular sign displays the number "20". Behind the bridge, lush greenery includes several palm trees on the left bank and a large tree with dense foliage overhanging the right side. In the distance, white multi-story buildings are visible through the trees. The water reflects the blue sky in the center of the arch but is dark and shadowed beneath the bridge structure, with gentle ripples visible on the surface.</t>
+A light gray concrete arch bridge spans a body of murky, olive-green water under a bright blue sky scattered with white clouds. The bridge features a single, rounded arch with a decorative, vertically fluted concrete element centered on the arch's apex, and vertical grooves run down the side walls. To the far left, a white rectangular sign with the number "20" is visible. Flanking the bridge on both sides are clusters of palm trees and dense green foliage. In the background, beyond the tree line, white multi-story buildings can be seen. The water beneath the bridge is dark and shadowed, while the surface outside the arch reflects the sky and the bridge structure.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -4404,7 +4491,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -4419,24 +4506,24 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
           <t>4.33</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>4.33</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>2.0</t>
@@ -4444,32 +4531,32 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.8232</t>
+          <t>0.8196</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1.5761</t>
+          <t>1.8204</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0.6479</t>
+          <t>0.6151</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>0.3838</t>
+          <t>0.3493</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>0.2047</t>
+          <t>0.2131</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>0.3576</t>
+          <t>0.3459</t>
         </is>
       </c>
     </row>
@@ -4498,66 +4585,62 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>The user wants a detailed description of the provided image.
+          <t>Thinking: The user wants a detailed description of the image.
 1.  **Identify the main subjects:**
-    *   On the left: A glowing, rectangular tunnel effect made of neon lights.
-    *   On the right: A vertical stack of playing cards, also glowing with neon light.
-2.  **Analyze the left element (Neon Tunnel):**
-    *   It's a rectangular shape.
-    *   It looks like a tunnel or a perspective view receding into the distance.
-    *   It's composed of concentric rectangles.
-    *   The color is a bright cyan/blue.
-    *   The lines are segmented, looking like LED strips or individual light bulbs connected in a line.
-    *   The perspective creates a vanishing point in the center.
+    *   Left side: A glowing, rectangular tunnel effect made of neon-like lines.
+    *   Right side: A vertical cascade of playing cards, also glowing.
+2.  **Analyze the "Tunnel" (Left):**
+    *   It's a series of concentric rectangles.
+    *   The lines are bright cyan/blue.
+    *   It creates a perspective effect, looking like a tunnel receding into the distance.
+    *   The lines are segmented, looking like LED strips or pixelated light.
     *   The background is pitch black.
-3.  **Analyze the right element (Playing Cards):**
-    *   There is a vertical column of cards.
-    *   They are arranged in a slightly staggered, overlapping manner, falling or stacked downwards.
-    *   The cards are illuminated with a blue neon glow, similar to the tunnel but distinct.
-    *   I need to identify the specific cards visible from top to bottom.
-        *   Top card: Looks like a 4 of Clubs (partially cut off at the very top). Wait, let's look closer. The top visible card has a '4' and clubs.
+3.  **Analyze the "Cards" (Right):**
+    *   They are arranged in a vertical, slightly staggered column.
+    *   They are glowing blue/cyan, matching the tunnel.
+    *   I need to identify the specific cards visible.
+        *   Top card: Looks like a 4 of Clubs (partially cut off).
         *   Next down: 4 of Hearts.
-        *   Next down: 6 of Spades.
+        *   Next down: 9 of Spades.
         *   Next down: 2 of Diamonds.
         *   Next down: 8 of Clubs.
         *   Next down: 7 of Spades.
         *   Bottom card: 3 of Clubs (partially visible).
-    *   Wait, let me re-examine the cards carefully.
-        *   Topmost visible card: 4 of Clubs.
+    *   Wait, let me look closer at the suits and numbers.
+        *   Top right corner: 4 of Clubs.
         *   Below that: 4 of Hearts.
-        *   Below that: 6 of Spades.
+        *   Below that: 9 of Spades.
         *   Below that: 2 of Diamonds.
         *   Below that: 8 of Clubs.
         *   Below that: 7 of Spades.
         *   Bottom: 3 of Clubs.
-    *   The cards are dark blue/black with white symbols, but the edges and symbols are glowing blue.
-4.  **Analyze the setting/background:**
-    *   The background is completely black, suggesting a dark room or a studio setup.
-    *   There is a faint vertical light strip on the far right edge, behind the cards.
-    *   There's a small, indistinct object near the top right, possibly a power outlet or a small device, but it's very dark and hard to define. I'll stick to describing the visible light strip.
-5.  **Synthesize the description:**
-    *   Start with the overall scene: A dark background featuring two distinct neon-lit elements.
-    *   Describe the left element: A rectangular neon tunnel. Mention the concentric rectangles, the cyan color, the perspective receding into the center, and the segmented nature of the light.
-    *   Describe the right element: A vertical cascade of playing cards. Mention the blue glow. List the cards from top to bottom as clearly as possible.
-    *   Mention the lighting: The primary light source is the neon itself, casting a glow on the cards and the tunnel. The rest is shadow.
-6.  **Refine the details:**
-    *   Left side: "rectangular tunnel of concentric, glowing cyan neon lines." "Perspective creates a vanishing point."
-    *   Right side: "vertical arrangement of playing cards." "Glowing blue edges."
-    *   Card details:
-        *   Top: 4 of Clubs.
-        *   Second: 4 of Hearts.
-        *   Third: 6 of Spades.
-        *   Fourth: 2 of Diamonds.
-        *   Fifth: 8 of Clubs.
-        *   Sixth: 7 of Spades.
-        *   Bottom: 3 of Clubs.
-    *   Wait, looking really closely at the bottom card... it looks like a 3 of Clubs.
-    *   Looking at the card above the 7 of Spades... it's an 8 of Clubs.
-    *   Looking at the card above that... it's a 2 of Diamonds.
-    *   Looking at the card above that... it's a 6 of Spades.
-    *   Looking at the card above that... it's a 4 of Hearts.
-    *   Looking at the very top... it's a 4 of Clubs.
-7.  **Final Polish:** Ensure the tone is objective</t>
+    *   The cards are angled slightly, creating a sense of falling or floating.
+4.  **Analyze the background and lighting:**
+    *   The background is completely black, emphasizing the glow.
+    *   The light source seems to be coming from the objects themselves (backlit or edge-lit).
+    *   There is a faint vertical light strip on the far right edge.
+5.  **Drafting the description (mental outline):**
+    *   Start with the overall scene: dark background, glowing elements.
+    *   Describe the left element: rectangular neon tunnel, concentric rectangles, cyan color, perspective.
+    *   Describe the right element: vertical stack of playing cards, glowing blue, specific card values and suits.
+    *   Mention the spatial relationship: tunnel on left, cards on right.
+6.  **Refining the details:**
+    *   The tunnel lines are distinct, segmented segments.
+    *   The cards have a blue glow around their edges and on the pips/symbols.
+    *   The cards are overlapping slightly.
+7.  **Final Polish (incorporating into the final output):**
+    *   "Against a pitch-black background, two distinct glowing elements are visible."
+    *   "On the left, a rectangular tunnel effect is formed by concentric, glowing cyan lines..."
+    *   "On the right, a vertical cascade of playing cards..."
+    *   List the cards: 4 of Clubs, 4 of Hearts, 9 of Spades, 2 of Diamonds, 8 of Clubs, 7 of Spades, 3 of Clubs.
+    *   Note the color consistency (cyan/blue).
+8.  **Final check against constraints:**
+    *   Single paragraph? Yes.
+    *   No bullet points? Yes.
+    *   No speculation? Yes.
+    *   Specific details? Yes.
+Let's write it out.
+Against a pitch-black background, two distinct glowing elements are arranged side-by-side. On the left, a rectangular tunnel effect is created by a series of concentric, glowing cyan lines that recede into the distance, forming a perspective of nested rectangles. The lines appear segmented, resembling LED strips or pixelated light, and emit a bright, cool blue-white hue. To the right, a vertical cascade of playing cards floats or falls in a staggered column, also illuminated with a matching blue glow. The visible cards, from top to bottom, include a 4 of Clubs, a 4 of Hearts, a 9 of Spades, a 2 of Diamonds, an 8 of Clubs, a 7 of Spades, and a partially visible 3 of Clubs at the bottom. The cards are angled slightly, overlapping one another, and their pips and indices are clearly visible in the same glowing blue tone as the tunnel. A faint vertical strip of light is visible on the far right edge of the frame</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -4572,7 +4655,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -4587,7 +4670,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -4597,12 +4680,12 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -4612,32 +4695,32 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.8009</t>
+          <t>0.7941</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.5194</t>
+          <t>1.5729</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0.8241</t>
+          <t>0.8221</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>0.3369</t>
+          <t>0.3568</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>0.1554</t>
+          <t>0.1714</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>0.3283</t>
+          <t>0.318</t>
         </is>
       </c>
     </row>
@@ -4665,31 +4748,43 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Thinking: The user wants a detailed description of the image provided.
-1.  **Identify the main subject:** It's a monster truck. Specifically, it looks like a Hot Wheels Monster Jam truck.
+          <t>Thinking: The user wants a detailed description of the image.
+1.  **Identify the main subject:** It's a monster truck, specifically the "Hot Wheels" truck.
 2.  **Analyze the truck's appearance:**
-    *   **Color/Design:** The body is primarily red with a colorful, graffiti-style design on the side (blue, yellow, red). The rear panel has a yellow and black hazard stripe pattern.
-    *   **Text/Logos:** "Hot Wheels" logo is visible on the rear panel (blue flame logo) and on the side. The number "68" is painted in white on the rear. "Monster Trucks" is written vertically on the side.
-    *   **Tires:** Massive, black, knobby tires. They dominate the lower portion of the image.
-    *   **Undercarriage:** The suspension is visible. It has red frame components and yellow shock absorbers/struts.
-    *   **Position:** The truck is angled slightly towards the right, showing the rear and left side.
+    *   **Color/Design:** The body is primarily red with a colorful, graffiti-style design. There are blue, yellow, and white elements.
+    *   **Text/Logos:** "Hot Wheels" logo is prominent on the rear panel (blue flame logo with red text) and on the side. The number "68" is painted in white on the rear. "Monster Trucks" is written vertically on the side.
+    *   **Tires:** Massive, black, knobby tires. They dominate the lower portion of the frame.
+    *   **Undercarriage:** The suspension is visible. It's red and yellow. The axles and shock absorbers are exposed.
+    *   **Condition:** It looks like a display model or a real truck on display, not necessarily in active competition right this second, given the tape.
 3.  **Analyze the setting/background:**
-    *   **Immediate surroundings:** The truck is sitting on a wooden platform or ramp. There is blue tape with logos strung across the foreground, acting as a barrier.
-    *   **Background:** There are blue banners with the "Hot Wheels" logo in yellow and red. Behind that, there are stadium-style seats (dark grey/black) and arena lighting.
-    *   **Other details:** A checkered flag is visible on the right side in the background.
-4.  **Drafting the description (incorporating spatial relationships and details):**
-    *   Start with the truck: A large monster truck dominates the frame, positioned at an angle showing its rear and left side.
-    *   Describe the body: The bodywork is painted bright red with a vibrant, multi-colored graphic design on the side featuring blues, yellows, and reds. The rear panel features a yellow and black diagonal hazard stripe pattern.
-    *   Specific markings: The "Hot Wheels" logo in its signature blue flame font is centered on the rear panel, next to the number "68" painted in white. The words "Monster Trucks" are visible vertically on the side panel.
-    *   Describe the mechanical parts: Massive, black, treaded tires are prominent in the foreground. The undercarriage reveals a red chassis frame and yellow suspension components, including shock absorbers.
-    *   Describe the foreground: A strip of blue tape with repeating logos runs horizontally across the lower middle of the image, separating the viewer from the vehicle. The truck rests on a wooden platform.
-    *   Describe the background: Behind the truck, large blue banners display the "Hot Wheels" logo in yellow and red. Further back, dark stadium seating and arena infrastructure are visible, along with a checkered flag standing on the right side.
-5.  **Refining and Polishing:** Ensure the tone is objective and descriptive. Check against constraints (no bullet points, no speculation).
-    *   *Self-Correction during drafting:* Make sure to mention the specific number "68". Note the "Monster Trucks" text. Clarify the tape is blue.
-6.  **Final Output Generation:** (This matches the thought process above).
-A large monster truck dominates the foreground, angled slightly to the right to display its rear and left side. The vehicle features a bright red body with a vibrant, graffiti-style graphic design on the side incorporating blues, yellows, and reds. The rear panel is decorated with a yellow and black diagonal hazard stripe pattern, featuring the "Hot Wheels" logo in its signature blue flame font alongside the number "68" painted in white. The words "Monster Trucks" are visible in black text vertically along the side panel.
-The truck sits on massive, black, knobby tires that fill the lower portion of the frame. The undercarriage is exposed, revealing a red chassis frame and yellow suspension components, including shock absorbers and linkages. A strip of blue tape with repeating logos runs horizontally across the lower middle of the image, acting as a barrier in front of the vehicle. The truck rests on a wooden platform.
-In the background, large blue banners display the "Hot Wheels" logo in yellow and red. Behind the banners, dark stadium seating and arena lighting structures are visible. To the right, a checkered flag stands upright near the rear of the truck.</t>
+    *   **Location:** Looks like an indoor arena or convention center. There are tiered seating areas in the background (dark, empty).
+    *   **Barriers:** Blue tarps or banners with the "Hot Wheels" logo are behind the truck.
+    *   **Flooring:** The truck is on a wooden platform or stage.
+    *   **Restrictions:** Blue caution tape with the Hot Wheels logo runs horizontally across the foreground, separating the viewer from the truck.
+    *   **Other details:** A checkered flag is visible on the right side.
+4.  **Structure the description:**
+    *   Start with the main subject (the truck) and its most striking features (tires, rear design).
+    *   Move to the details of the truck's body (colors, logos, number).
+    *   Describe the undercarriage/suspension.
+    *   Describe the immediate surroundings (tape, platform).
+    *   Describe the background (banners, arena seating).
+5.  **Drafting the content (mental or scratchpad):**
+    *   *Truck:* Red body, "Hot Wheels" logo on back, number 68. Huge black tires. Yellow and red suspension.
+    *   *Background:* Blue banners with "Hot Wheels". Arena seats above.
+    *   *Foreground:* Blue tape. Wooden floor.
+6.  **Refining and Polishing (adhering to guidelines):**
+    *   *Specifics:* Mention the "Monster Trucks" text. Note the checkered flag. Describe the tire tread.
+    *   *Spatial:* The truck is angled slightly away from the camera, showing the rear and right side. The tape is in front. The banners are behind.
+    *   *No speculation:* Don't say "it's waiting for a race." Just say it's on display.
+7.  **Final Review against constraints:**
+    *   Single paragraph? Yes.
+    *   No bullet points? Yes.
+    *   No "This image shows"? Yes.
+    *   Accurate? Yes.
+Let's write it out.
+"A large monster truck, identified by the 'Hot Wheels' branding, dominates the foreground, angled slightly to the right to reveal its rear and passenger side. The truck features a vibrant, graffiti-style paint job primarily in red, with accents of blue, yellow, and white. The rear panel displays a large 'Hot Wheels' logo in blue and red alongside the number '68' in white, while the side of the cab features the words 'Monster Trucks' in yellow lettering. The vehicle is equipped with massive, black, knobby tires that are significantly larger than the body, resting on a wooden platform. The exposed undercarriage reveals a complex suspension system with red and yellow components, including shock absorbers and axles. A strip of blue caution tape with the Hot Wheels logo runs horizontally across the lower middle of the frame, separating the vehicle from the viewer. Behind the truck, blue barriers display the 'Hot Wheels' logo in yellow and red. In the background, the upper levels of an indoor arena are visible, featuring dark, tiered seating and structural beams, while a checkered flag stands vertically to the right of the truck."
+Looks good. Fits all criteria.
+A large monster truck, identified by the "Hot Wheels" branding, dominates the foreground, angled slightly to the right to reveal its rear and passenger side. The truck features a vibrant, graffiti-style paint job primarily in red, with accents of blue, yellow, and white. The rear panel displays a large "Hot Wheels" logo in blue and red alongside the number "68" in white, while the side of the cab features</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -4724,12 +4819,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -4744,32 +4839,32 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0.8235</t>
+          <t>0.8112</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1.7001</t>
+          <t>1.5133</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.7192</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>0.3735</t>
+          <t>0.3737</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>0.2116</t>
+          <t>0.2012</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>0.4451</t>
+          <t>0.4346</t>
         </is>
       </c>
     </row>
@@ -4796,38 +4891,43 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Thinking: The user wants a detailed description of the image.
-1.  **Identify the main subject:** The central focus is the iconic "Flamingo" sign, specifically the large flamingo head structure illuminated at night.
+          <t>The user wants a detailed description of the image.
+1.  **Identify the main subject:** The most prominent feature is the large, illuminated sign for the "Flamingo" hotel/casino. It's a giant flamingo head structure.
 2.  **Analyze the sign:**
-    *   **Text:** "Flamingo" is written in a cursive, gold, illuminated font at the top.
-    *   **Structure:** Below the text is a large, stylized flamingo head. It's constructed with red and orange lights forming the beak and face, and white/yellow lights outlining the feathers and neck. The beak is open, pointing slightly left.
-    *   **Lighting:** The sign is brightly lit against the night sky. The colors are predominantly red, orange, and white/yellow.
+    *   **Text:** "Flamingo" in cursive, gold/yellow neon lights at the top.
+    *   **Structure:** A large, stylized flamingo head. The beak is red/orange with horizontal lines. The neck and head are outlined in white/yellow lights. The feathers (wings/neck feathers) are spiky and outlined in white lights.
+    *   **Position:** It's in the foreground, slightly right of center.
 3.  **Analyze the background:**
-    *   **Building:** Behind the sign is a massive, multi-story hotel/casino building. It has a grid-like facade with many windows.
-    *   **Color:** The building is bathed in purple/pink lighting.
-    *   **Text on building:** There is faint, reversed text visible on the building facade, reading "THE COSMOPOLITAN".
-4.  **Analyze the foreground/surroundings:**
-    *   **Palm trees:** Several palm trees are visible in the foreground, silhouetted against the lights. One is prominent on the left, another on the far right.
-    *   **Lower level:** Below the flamingo sign, there is a lower structure with blue neon trim.
-    *   **Signage:** To the right, there is a smaller sign that says "WAYNE UP CLOSE AND PERSONAL" with a picture of a man.
-    *   **Other lights:** There are strings of lights hanging vertically on the right side of the building.
-5.  **Synthesize the description:**
-    *   Start with the main subject: The illuminated Flamingo sign.
-    *   Describe the sign's details: "Flamingo" text, the flamingo head structure, colors (red, orange, white lights).
-    *   Move to the background: The large hotel building, purple lighting, "The Cosmopolitan" text.
-    *   Describe the foreground elements: Palm trees, the lower entrance area with blue lights, the "Wayne" sign.
-    *   Mention the overall atmosphere: Nighttime, vibrant, Las Vegas style.
-**Drafting the description:**
-The image captures a vibrant nighttime scene dominated by the iconic illuminated sign of the Flamingo hotel and casino. At the center, a large, stylized flamingo head structure glows brightly. The word "Flamingo" is displayed in a cursive, gold-colored font at the top of the structure. Below the text, the flamingo's head and neck are formed by a complex arrangement of lights; the beak and face area feature horizontal red and orange stripes, while the feathers and outline are traced with bright white and yellow bulbs.
-Behind this sign stands a massive, multi-story building with a grid-like facade of windows, bathed in a soft purple and pink ambient light. Faint, reversed white lettering on the building's facade reads "THE COSMOPOLITAN." To the right of the main sign, vertical strings of lights hang down the side of the building.
-In the foreground, silhouetted palm trees frame the scene on the left and right. Below the flamingo sign, the lower level of the building features a facade with blue neon trim and rows of small, square lights. On the far right, a smaller digital sign displays the name "WAYNE" in large letters above the text "UP CLOSE AND PERSONAL," accompanied by a small image of a man. The overall scene is a colorful display of neon and architectural lighting typical of a Las Vegas strip at night.
-**Refining:**
-- Ensure spatial relationships are clear (behind, below, to the right).
-- Check for specific details (colors, text).
-- Make sure it flows well.
-The draft looks good. I will finalize it based on these observations.
-This image captures a vibrant nighttime view of the iconic Flamingo sign, set against the backdrop of a large hotel building. Dominating the center is a massive, illuminated structure shaped like a flamingo's head. At the top, the word "Flamingo" is written in a cursive, gold-colored font. Below the text, the flamingo's head and neck are constructed from a framework of lights; the beak and face area features horizontal stripes of red and orange lights, while the feathers and outline are traced with bright white and yellow bulbs.
-Behind the sign stands a towering, multi-story building with a grid-like facade of windows, bathed in a soft purple and pink ambient light. Faint</t>
+    *   **Building:** A massive, multi-story hotel building rises behind the sign. It has a grid-like facade of windows.
+    *   **Lighting:** The building is bathed in purple/pinkish light. Some windows are lit from within.
+    *   **Text on building:** There is faint, reversed text on the building that reads "THE COSMOPOLITAN" (though it's upside down/reversed relative to the viewer, likely on the opposite side of the building). Wait, looking closer at the reversed text, it says "THE COSMOPOLITAN". This suggests the photo might be taken from across the street or the building is angled. Actually, looking very closely at the top left, the text "THE COSMOPOLITAN" is visible but reversed, indicating it's on the side of the building facing away or it's a reflection. No, wait, it's just text on the building. Let's look closer. It says "THE COSMOPOLITAN" but it's upside down and reversed. This is likely the Cosmopolitan of Las Vegas building right next to the Flamingo.
+4.  **Analyze the lower section:**
+    *   **Entrance area:** Below the flamingo sign, there's a lower structure.
+    *   **Signage:** To the right, there's a marquee for "WAYNE" with the tagline "UP CLOSE AND PERSONAL". It features a picture of a man (Wayne Newton).
+    *   **Lighting:** Blue neon strips run along the top of this lower section.
+    *   **Windows:** There are rows of small, square lights (like a grid of bulbs) on the wall below the flamingo.
+5.  **Analyze the surroundings:**
+    *   **Trees:** Palm trees are visible on the left and right edges, framing the shot.
+    *   **Sky:** It's night time.
+6.  **Synthesize the description:**
+    *   Start with the main subject: The Flamingo sign. Describe the flamingo head, the colors (red beak, white outline), and the "Flamingo" text.
+    *   Move to the background: The tall hotel building with purple lighting. Mention the reversed text "THE COSMOPOLITAN".
+    *   Describe the foreground/lower area: The entrance area, the "WAYNE" marquee, the blue lights, the grid of small lights.
+    *   Mention the palm trees.
+Refining the description:
+- The sign is a giant flamingo head.
+- The beak is red with horizontal lines.
+- The neck and feathers are outlined in bright white/yellow bulbs.
+- The word "Flamingo" is in script above it.
+- Behind it is a tall building with a grid of windows, illuminated in purple.
+- On the building, reversed text reads "THE COSMOPOLITAN".
+- Below the flamingo is a lower facade with blue neon trim.
+- To the right, a marquee reads "WAYNE UP CLOSE AND PERSONAL".
+- Palm trees frame the left and right sides.
+Let's double check the reversed text. Yes, "THE COSMOPOLITAN" is visible on the upper left side of the building, appearing reversed. This confirms the location context (Las Vegas Strip).
+Final Polish: Ensure the flow is logical (top to bottom, main subject to background).
+*   **Main Subject:** The iconic Flamingo sign. A large, illuminated flamingo head. The beak is red/orange with horizontal striations. The neck and head are outlined in bright white/yellow lights. The word "Flamingo" is written in cursive script above the head in similar yellow lights.
+*   **Background:** A massive high-rise building looms behind the sign. It has a grid of dark windows, many lit from inside. The building is washed in purple light. On the upper left facade, the words "</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -4842,7 +4942,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -4857,17 +4957,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -4877,37 +4977,37 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.8145</t>
+          <t>0.8181</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.8509</t>
+          <t>0.8244</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0.7124</t>
+          <t>0.8126</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>0.3134</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>0.1473</t>
+          <t>0.1564</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>0.2945</t>
+          <t>0.3314</t>
         </is>
       </c>
     </row>
@@ -4937,35 +5037,36 @@
           <t>Thinking: The user wants a detailed description of the provided image.
 1.  **Identify the main subject:** The primary focus is a concrete floor with numbers written on it.
 2.  **Analyze the numbers:**
-    *   There are three distinct markings.
-    *   On the left, there is a number "3" with a vertical line above it, resembling a tally mark or a specific notation.
-    *   In the center, there is a number "2" with a vertical line above it.
-    *   On the right, there is a faint vertical line, possibly a "1" or just a mark, but it's less distinct. Wait, looking closer, it looks like a vertical line, maybe a "1" or just a tick mark. Let's describe it as a vertical line or faint marking. Actually, looking very closely at the rightmost mark, it's just a vertical line.
-3.  **Analyze the surroundings:**
-    *   **Top Left:** A dark green box or container. It has some yellow dots and faint white markings (maybe text or lines) on it.
-    *   **Top Right:** A wooden spool or reel. It has a black handle or lever attached to it.
-    *   **Far Right Edge:** A piece of wood or a post, partially visible.
-    *   **Floor:** Grey concrete. It has a seam running horizontally across the upper third. There are some stains and debris on the floor.
-4.  **Lighting:** The lighting seems artificial, casting a shadow from the top right object towards the left. The floor is relatively evenly lit but has some glare.
-5.  **Composition:** High-angle shot looking down at the floor.
-**Drafting the description:**
-*   Start with the floor and the numbers. "A high-angle, close-up shot captures a grey concrete floor..."
-*   Describe the numbers. "...marked with handwritten numbers in dark grey or black chalk or paint."
-*   Detail the specific numbers. "On the left side, the number '3' is written with a vertical line above it. In the center, the number '2' is written with a vertical line above it. To the right, a faint vertical line is visible."
-*   Describe the objects at the top. "In the upper left corner, the bottom edge of a dark green box or container is visible, featuring small yellow dots and faint white markings."
-*   Describe the object in the top right. "In the upper right corner, a portion of a wooden spool or reel is seen, with a black handle extending from it."
-*   Mention the floor details. "A horizontal seam runs across the concrete near the top. The floor surface shows signs of wear, with small stains, debris, and a faint shadow cast across the right side."
-**Refining:**
-*   Make sure to mention the spatial relationships. The numbers are arranged horizontally. The box is above the '3'. The spool is above the right side.
-*   Check for accuracy. The vertical lines above the numbers look like tally marks or perhaps indicating a specific measurement or count. I will describe them as vertical lines above the numbers.
-*   The rightmost mark is just a vertical line. It might be a '1' but it's very faint. I'll describe it as a vertical line.
-**Final Polish:**
-"A high-angle, close-up view shows a grey concrete floor marked with handwritten numbers. In the foreground, the number '3' is written on the left, with a vertical line above it. To its right, the number '2' is written, also with a vertical line above it. Further to the right, a faint vertical line is visible on the floor. A horizontal seam runs across the concrete near the top of the frame. In the upper left corner, the bottom edge of a dark green box or container is visible, decorated with small yellow dots and faint white markings. In the upper right corner, a section of a wooden spool or reel is partially visible, featuring a black handle. The floor surface is textured with minor stains, debris, and a soft shadow cast across the right side."
-Let's double check the rightmost mark. It looks like a vertical line. It's distinct enough to be a mark.
-Let's check the box. It looks like a cardboard box painted green or a plastic bin. "Dark green box or container" is safe.
-Let's check the spool. "Wooden spool or reel" is accurate.
-The description looks solid.
-A high-angle, close-up view captures a grey concrete floor marked with handwritten numbers in dark grey or black. In the lower left area, the number "3" is written with a vertical line above it. To its right, in the center, the number "2" is written, also topped with a vertical line. Further</t>
+    *   There is a number "3" on the left. Above it is a small vertical mark, possibly a "1" or just a scratch.
+    *   There is a number "2" in the center. Above it is a similar small vertical mark.
+    *   To the right of the "2", there is a faint, vertical line or mark that looks like a "1" or a tally mark, but it's very indistinct.
+    *   The numbers appear to be written in chalk or a dark marker directly on the concrete. They are somewhat faded.
+3.  **Analyze the background/surroundings:**
+    *   **Top Left:** A dark green box or container. It has some yellow dots and faint white markings (maybe text or a logo) on it. It looks like a cardboard box painted green or a plastic bin.
+    *   **Top Right:** A wooden spool or reel. It's light brown wood. There's a black cable or cord resting on it. Next to it is a piece of white, possibly painted wood or a block.
+    *   **Floor:** The floor is grey concrete. It has a visible seam or crack running horizontally across the upper third of the image. There are some stains and debris scattered around.
+    *   **Lighting:** The lighting seems artificial, casting a shadow from the top right towards the bottom left, suggesting a light source from the upper right. The right side of the floor is brighter.
+4.  **Drafting the description (mental outline):**
+    *   Start with the floor and the numbers.
+    *   Mention the specific numbers: "3" and "2" with marks above them.
+    *   Describe the faint mark to the right.
+    *   Move to the top edge objects: the green box on the left, the wooden spool on the right.
+    *   Describe the floor texture and the horizontal seam.
+5.  **Refining the description (adding detail and precision):**
+    *   *Numbers:* "Handwritten numbers '3' and '2' are visible on the grey concrete floor." "Above the '3' is a small vertical dash." "Above the '2' is a similar vertical dash." "To the right of the '2', a faint, vertical line is visible."
+    *   *Objects:* "In the upper left corner, the bottom edge of a dark green box or container is visible." "It features small yellow dots and faint white markings." "In the upper right corner, a portion of a wooden cable spool is seen." "A black cable rests on the spool." "Next to the spool is a piece of white, weathered wood."
+    *   *Floor details:* "A horizontal seam runs across the upper portion of the floor." "The concrete surface shows signs of wear, with small stains and debris."
+6.  **Final Polish (combining into a cohesive paragraph):**
+    A high-angle, close-up shot captures a section of a grey concrete floor marked with handwritten numbers. In the lower left quadrant, the number "3" is written in dark, chalk-like markings, with a small vertical dash positioned directly above it. To the right of that, the number "2" is similarly inscribed, also topped with a small vertical dash. Further to the right, a faint, vertical line is visible on the concrete. A horizontal seam or crack runs across the upper third of the floor. In the top left corner, the bottom edge of a dark green box or container is visible, decorated with small yellow dots and faint white markings. In the top right corner, a portion of a wooden cable spool appears, with a black cable resting on its edge, alongside a piece of white, weathered wood. The lighting casts a shadow across the right side of the floor, highlighting the texture of the concrete.
+7.  **Final Review against constraints:**
+    *   Single detailed caption? Yes.
+    *   Main subject first? Yes (floor/numbers).
+    *   Specific/precise? Yes.
+    *   Spatial relationships? Yes (left, right, top).
+    *   No speculation? Yes.
+    *   No bullet points? Yes.
+This looks good. I will output this description.
+A high-angle, close-up shot captures a section of a grey concrete floor marked with handwritten numbers. In the lower left quadrant, the number "3" is written in dark, chalk-like markings, with a small vertical dash positioned directly above it. To the right of that, the number "2" is similarly inscribed, also topped with</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -4980,7 +5081,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4995,57 +5096,57 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
           <t>3.67</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>4.67</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>3.67</t>
-        </is>
-      </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.8225</t>
+          <t>0.8187</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.943</t>
+          <t>0.8854</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0.8402</t>
+          <t>0.7663</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>0.2398</t>
+          <t>0.2318</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>0.1014</t>
+          <t>0.1129</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>0.1533</t>
+          <t>0.1506</t>
         </is>
       </c>
     </row>
@@ -5074,54 +5175,54 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Thinking: The user wants a detailed description of the image.
-1.  **Identify the main subject:** The image shows two silhouettes projected onto a wall. They appear to be people engaged in some kind of physical activity, possibly dancing or playing a game.
+          <t>The user wants a detailed description of the image.
+1.  **Identify the main subject:** The image shows two silhouettes projected onto a wall. They appear to be people in motion, possibly dancing or playing.
 2.  **Analyze the left figure:**
     *   It's a silhouette of a person.
-    *   They are facing somewhat towards the right but angled slightly away.
-    *   Their arms are outstretched, reaching forward and slightly up.
-    *   Their legs are bent, suggesting movement or a stance.
-    *   The silhouette is reddish-brown/pinkish against the background.
+    *   The figure is facing somewhat right but angled towards the center.
+    *   Both arms are extended outwards, slightly bent at the elbows. The left arm is higher than the right.
+    *   The head is visible, with what looks like hair or a hat.
+    *   The body is upright but slightly leaning.
+    *   The legs are partially visible, suggesting a standing or stepping pose.
 3.  **Analyze the right figure:**
     *   It's a silhouette of a person.
-    *   They are in a dynamic pose, possibly kicking or jumping.
-    *   One leg is extended high in the air (left leg).
-    *   One arm is raised high (right arm).
-    *   The other arm is down by their side.
-    *   This silhouette is also reddish-brown/pinkish.
+    *   This figure is in a more dynamic pose, appearing to be mid-jump or mid-kick.
+    *   The right arm is raised high above the head.
+    *   The left arm is down by the side.
+    *   The right leg is extended forward and slightly up, as if kicking or stepping high.
+    *   The left leg is bent, supporting the body.
+    *   The figure is facing somewhat left/forward.
 4.  **Analyze the background/surface:**
-    *   It looks like a large, flat surface, likely a wall or a screen.
-    *   The color is a pale, yellowish-green or chartreuse.
-    *   There are vertical seams or lines running down the surface, suggesting it might be made of panels or boards.
+    *   The surface is a large, flat wall.
+    *   It has a yellowish-green tint, likely due to lighting or projection color.
+    *   There are vertical seams or lines running down the wall, suggesting it might be made of panels or boards.
     *   There are small dark dots or marks along these vertical lines, possibly screws or fasteners.
-    *   There is a faint, blurry reddish glow near the top center, above the left figure's head.
+    *   There is a reddish glow near the top left, above the left figure's head.
+    *   There is a small, dark rectangular object on the far right edge, possibly a switch or outlet.
 5.  **Analyze the foreground/bottom:**
-    *   At the very bottom, there is a dark, shadowed area. It looks like the edge of a stage, a floor, or perhaps a dark wall below the projection surface. It's a solid dark brown/black band.
-6.  **Lighting and Atmosphere:**
-    *   The lighting is dim, typical of a projection environment.
-    *   The projection itself casts a warm, reddish hue on the figures.
-    *   The overall image has a slightly grainy or low-resolution quality.
-7.  **Spatial Relationships:**
-    *   The left figure is positioned on the left side of the frame.
-    *   The right figure is positioned on the right side of the frame.
-    *   They are separated by a significant gap in the middle of the wall.
-    *   The dark area is below both figures.
+    *   At the very bottom, there is a dark, shadowed area. It looks like the top of a piece of furniture or a ledge, possibly a piano or a low wall, running horizontally across the frame. It has a reddish-brown edge.
+6.  **Lighting and Color:**
+    *   The overall lighting is dim and hazy.
+    *   The projection casts reddish/pinkish shadows on the yellowish wall.
+    *   The silhouettes are dark, almost black, but with reddish hues where the light hits them.
+    *   The image has a grainy texture.
 **Drafting the description:**
 Start with the main subject: Two silhouettes projected on a wall.
-Describe the left figure: A person with arms outstretched, legs bent.
-Describe the right figure: A person in a dynamic pose, leg kicked up, arm raised.
-Describe the background: Pale yellow-green wall with vertical seams.
-Describe the bottom: Dark shadowed area.
-Refine details: Mention the reddish tint of the silhouettes. Mention the faint red glow.
-**Refining the description for flow and accuracy:**
-"A low-angle shot captures two reddish-brown silhouettes projected onto a large, pale yellow-green wall." -&gt; Good start.
-"The figure on the left stands with both arms extended forward and slightly upward, while their legs are bent in a stance." -&gt; Accurate.
-"To the right, a second figure is captured in a dynamic, mid-motion pose, with one leg kicked high into the air and one arm reaching upward." -&gt; Accurate.
-"The wall surface appears to be constructed of panels, indicated by faint vertical seams running down the center and right side, marked by small dark fasteners." -&gt; Good detail.
-"A faint, blurry red light glows near the top center of the wall, above the left figure." -&gt; Notable attribute.
-"The bottom of the image is dominated by a dark, shadowed area, likely the floor or a lower wall section, contrasting with the illuminated projection surface." -&gt; Context.
+Describe the left figure: A person with arms outstretched.
+Describe the right figure: A person in a dynamic pose, leg raised, arm up.
+Describe the wall: Yellowish-green, vertical seams, fasteners.
+Describe the bottom: Dark ledge/furniture.
+Mention the lighting: Reddish glow, hazy.
+**Refining the description:**
+"A dimly lit scene features two human silhouettes projected onto a large, pale yellow-green wall."
+"The figure on the left stands with both arms extended outward and slightly upward, fingers splayed, appearing to reach or balance."
+"The figure on the right is captured in a dynamic, mid-motion pose, with the right leg kicked high into the air and the right arm raised straight up above the head."
+"The wall surface shows vertical seams with small, dark fasteners or screws running down its length."
+"A faint reddish glow is visible near the top left, above the first figure's head."
+"At the bottom of the frame, a dark, shadowed horizontal surface, possibly the top of a piano or a ledge, runs across the width of the image."
+"The overall image has a grainy quality, suggesting a low-light photograph of a projection."
 Let's combine and polish.
-Two reddish-brown silhouettes are projected onto a large, pale yellow-green wall, appearing to depict people in motion. On the left, a figure stands with both arms extended forward and slightly upward, legs bent in a stance that suggests reaching or balancing. To the right, a second figure is captured in a dynamic pose, with one leg kicked high into the air and one arm reaching upward, while the other arm hangs by their side. The wall surface features faint vertical seams running down its length, marked by small, dark fasteners or screws. A faint, blurry red glow is visible near the top center of the wall, just above the head of the left figure. The bottom portion of the image is obscured by a dark, shadowed area, likely</t>
+"The image displays two human silhouettes projected onto a large, pale yellow-green wall. The figure on the left is standing with both arms extended outward and slightly upward, fingers splayed as if reaching or balancing. The figure on the right is captured in a dynamic, mid-motion pose, appearing to kick or leap, with the right leg extended high and the right arm raised straight up above the head. The wall surface features vertical seams running from top to bottom, marked by small, dark fasteners or screws. A faint, diffuse reddish glow is visible near the top left, just above the head of the left figure. At the very bottom of the frame, a dark, shadowed horizontal structure, possibly the top edge of a piano or a low wall, runs across the foreground. The lighting is dim and hazy, casting reddish hues onto the sil</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -5171,37 +5272,37 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.8219</t>
+          <t>0.8208</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.9161</t>
+          <t>0.7598</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0.7635</t>
+          <t>0.8578</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>0.3473</t>
+          <t>0.3345</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>0.1709</t>
+          <t>0.1584</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>0.3001</t>
+          <t>0.2928</t>
         </is>
       </c>
     </row>
@@ -5229,33 +5330,31 @@
       <c r="E20" t="inlineStr">
         <is>
           <t>Thinking: The user wants a detailed description of the image.
-1.  **Identify the main subject:** It's a spider.
-    *   **Appearance:** It has a round, bulbous abdomen that is brownish-tan with some darker mottling. The cephalothorax (head area) is smaller and darker. The legs are long and spindly, with a mix of dark brown/black and lighter, possibly white or tan, banding or spots. The front legs look slightly reddish-brown.
-    *   **Position:** It is positioned centrally on a flat surface, facing slightly towards the left but mostly forward.
-2.  **Identify the surface:**
-    *   **Material:** Looks like a terracotta-colored tile or perhaps a painted wooden board. It has a rough, textured surface with speckles of dirt or wear.
-    *   **Color:** Rusty orange/terracotta with dark brown/black speckling and streaks.
-    *   **Edges:** On the left edge, there's a concrete or stone border with a circular hole or indentation.
-3.  **Identify the background:**
-    *   **Immediate background:** Blurry. There are green leaves, suggesting a plant or vine.
-    *   **Further background:** A white structure, possibly siding or a wall. There's a dark horizontal bar at the very top, likely a railing or beam.
-    *   **Lighting:** Natural daylight, casting soft shadows. The light seems to be coming from above.
-4.  **Drafting the description (mental outline):**
-    *   Start with the spider on the tile.
-    *   Describe the spider's body parts (abdomen, legs, color).
-    *   Describe the tile surface (color, texture, edge).
-    *   Describe the background (blurry leaves, white wall, dark bar).
-5.  **Refining the description (incorporating specific details):**
-    *   *Spider:* A medium-sized spider with a round, tan-brown abdomen sits in the center. Its legs are long and jointed, showing a pattern of dark and light bands. The front legs have a reddish hue.
-    *   *Surface:* It rests on a flat, rectangular surface that is reddish-brown or terracotta in color. The surface is textured with dark speckles and streaks, resembling weathered paint or a rough tile. To the left, a section of grey concrete or stone is visible with a circular hole.
-    *   *Background:* The background is out of focus. Behind the tile, there are green leaves and stems, suggesting vegetation. Further back, a white wall or siding is visible. A dark, horizontal beam runs across the very top edge of the frame.
-6.  **Final Polish (checking against constraints):**
-    *   No bullet points.
-    *   No speculation.
-    *   Fluent prose.
-    *Draft:* A medium-sized spider with a round, tan-brown abdomen and long, spindly legs rests centrally on a flat, reddish-brown surface. The spider's legs are banded with dark and light markings, while the front legs appear slightly reddish. The surface beneath it is textured and speckled with dark spots and streaks, resembling a weathered terracotta tile or painted wood. To the left edge of the frame, a section of grey concrete or stone is visible, featuring a circular indentation or hole. The background is out of focus, showing green foliage and stems behind the surface, with a white wall or siding visible further back. A dark, horizontal beam runs across the very top of the image.
-7.  **Final Review:** Does it cover everything? Yes. Is it accurate? Yes. Is it detailed? Yes.
-A medium-sized spider with a round, tan-brown abdomen and long, spindly legs rests centrally on a flat, reddish-brown surface. The spider's legs are banded with dark and light markings, while the front legs appear slightly reddish-brown. The surface beneath it is textured and speckled with dark spots and streaks, resembling a weathered terracotta tile or painted wood. To the left edge of the frame, a section of grey concrete or stone is visible, featuring a circular indentation or hole. The background is out of focus, showing green foliage and stems behind the surface, with a white wall or siding visible further back. A dark, horizontal beam runs across the very top of the image.</t>
+1.  **Identify the main subject:** It's a spider. It looks like an orb-weaver, possibly a *Araneus* species. It has a round abdomen and long legs.
+2.  **Describe the spider's appearance:**
+    *   **Abdomen:** Round, brownish-tan with some darker mottling or spots.
+    *   **Cephalothorax:** Smaller, darker, brownish.
+    *   **Legs:** Long, spindly. They have a distinct pattern: reddish-brown segments near the body, transitioning to black and white bands on the tips.
+    *   **Position:** It's facing slightly away from the camera, angled towards the left.
+3.  **Describe the surface:**
+    *   It's a flat, reddish-brown surface. Looks like a painted wooden beam or perhaps a brick ledge.
+    *   Texture: Rough, weathered. There are dark speckles, scratches, and patches of discoloration (dirt or wear).
+    *   Left edge: There's a concrete or stone edge visible on the far left, with a circular hole or indentation.
+4.  **Describe the background:**
+    *   It's out of focus (shallow depth of field).
+    *   Top left: Green foliage, leaves, maybe a tree trunk or branch.
+    *   Top right: White siding or wall, possibly part of a house. A thin wire or vine runs across it.
+5.  **Lighting:** Natural daylight. Shadows are soft, suggesting diffuse light. The spider casts a slight shadow on the surface.
+**Drafting the description:**
+A medium-sized spider with a round, brownish abdomen and long, banded legs rests on a weathered, reddish-brown wooden beam. The spider is positioned centrally but slightly to the right, facing towards the left. Its legs display a distinct pattern of reddish-brown segments near the body that transition into black and white bands at the tips. The surface beneath it is textured with dark speckles, scratches, and patches of grime, indicating age and exposure to the elements. To the far left, a section of rough, grey concrete or stone is visible, featuring a circular indentation. The background is softly blurred, showing green foliage and leaves in the upper left corner and white siding or wall panels in the upper right, with a thin, curved wire or vine stretching across the white surface. The lighting appears to be natural daylight, casting soft shadows beneath the spider.
+**Refining and checking constraints:**
+*   Single paragraph? Yes.
+*   No bullet points? Yes.
+*   Specific details? Yes (banded legs, weathered surface, background elements).
+*   No speculation? Yes.
+**Final Polish:**
+A medium-sized spider with a round, mottled brown abdomen and long, spindly legs rests on a weathered, reddish-brown wooden beam. The spider is positioned centrally, angled slightly toward the left, with its legs displaying a distinct pattern of reddish-brown segments near the body that transition into black and white bands at the tips. The surface beneath it is rough and textured, marked by dark speckles, scratches, and patches of discoloration. To the far left edge, a section of grey, concrete-like material is visible, featuring a circular hole or indentation. The background is out of focus, revealing green foliage and leaves in the upper left corner and white siding or wall panels in the upper right, with a thin, curved wire or vine stretching across the white surface. Natural daylight illuminates the scene, casting a subtle shadow beneath the spider.
+A medium-sized spider with a round, mottled brown abdomen and long, spindly legs rests on a weathered, reddish-brown wooden beam. The spider is positioned centrally, angled slightly toward the left, with its legs displaying a distinct pattern of reddish-brown segments near the body that transition into black and white bands at the tips. The surface beneath it is rough and textured, marked by dark speckles, scratches, and patches of discoloration. To the far left edge, a section of grey, concrete-like material is visible, featuring a circular hole or indentation. The background is out of focus, revealing green foliage and leaves in the upper left corner and white siding or wall panels in the upper right, with a thin, curved wire or vine stretching across the white surface. Natural daylight illuminates the scene, casting a subtle shadow beneath the spider.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -5270,7 +5369,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -5285,7 +5384,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -5295,47 +5394,47 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.7999</t>
+          <t>0.8077</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.6728</t>
+          <t>0.6398</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.6087</t>
+          <t>0.6743</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.2622</t>
+          <t>0.3018</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.1272</t>
+          <t>0.1363</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.2137</t>
+          <t>0.219</t>
         </is>
       </c>
     </row>
@@ -5362,37 +5461,39 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Thinking: The user wants a detailed description of the image.
-1.  **Identify the main subject:** A large, bright red bowl filled with yellow bananas.
+          <t>The user wants a detailed description of the image.
+1.  **Identify the main subject:** A large, bright red bowl filled with a bunch of yellow bananas.
 2.  **Analyze the bowl:**
     *   Color: Bright red.
     *   Material: Looks like plastic or ceramic, glossy.
-    *   Text/Logos: There's a black rectangular sticker or decal on the front with white text that reads "CRIME &amp; Vengeance" in a stylized, gothic font. To the left of the text, there is a purple butterfly sticker.
-    *   Position: Sitting on a dark, speckled countertop.
+    *   Decorations:
+        *   On the left side: A purple butterfly sticker or decal.
+        *   On the front: A black rectangular sticker with white text that reads "CRIME &amp; Vengeance" in a stylized, gothic font.
 3.  **Analyze the bananas:**
     *   Quantity: A bunch, roughly 5-6 visible fingers.
-    *   Color: Yellow with some green near the stems.
-    *   Stems: Brown, woody stems at the top.
-    *   Stickers: Small white stickers are visible on the skin of the bananas.
-4.  **Analyze the background/surroundings:**
+    *   Color: Yellow, some green near the stems.
+    *   Position: They are resting inside the bowl, stems pointing upwards and slightly towards the left.
+    *   Details: There are small stickers on the bananas (brand stickers).
+4.  **Analyze the background/setting:**
+    *   Surface: The bowl sits on a dark, speckled countertop (looks like granite or laminate).
     *   Left side: A clear plastic bag containing what looks like bread or pastries. Behind that, a black electronic device (maybe a card reader or register part) and a metal rack.
     *   Right side: A glass display case or window. Inside, there are blurry items, possibly food.
-    *   Top/Back: Metal racks, possibly for holding items.
-    *   Surface: Dark, possibly granite or laminate countertop.
-5.  **Lighting:** Indoor lighting, somewhat reflective on the bowl and bananas.
-6.  **Composition:** The bowl is central and in the foreground. The background is slightly out of focus.
+    *   Behind the bowl: Metal racks, possibly for holding items.
+5.  **Lighting:** Indoor lighting, somewhat harsh reflections on the red bowl and the bananas.
+6.  **Spatial relationships:** The bowl is central. The bananas are inside. The butterfly is to the left of the text. The bag is to the left of the bowl.
 **Drafting the description:**
 Start with the bowl and bananas.
-"A large, glossy red bowl sits centrally in the foreground, filled with a bunch of yellow bananas."
-Describe the bowl's details.
-"The bowl features a black rectangular decal on its front face with the white text 'CRIME &amp; Vengeance' in a stylized, gothic font. To the left of the text is a purple butterfly sticker."
-Describe the bananas.
-"The bananas are bright yellow with green tips near the stems and have small white stickers on their skins. They are clustered together, leaning slightly to the right."
-Describe the background.
-"To the left of the bowl, a clear plastic bag containing brown, bread-like items is visible, along with a black electronic device and metal shelving. To the right, a glass display case reflects the surroundings. The bowl rests on a dark, speckled countertop."
+"A large, glossy red bowl sits centrally on a dark, speckled countertop."
+"Inside the bowl is a bunch of yellow bananas with green stems, arranged with their tips pointing upward and slightly to the left."
+"Two small white stickers are visible on the bananas."
+"Adorning the exterior of the bowl are two distinct decals."
+"On the front right side, there is a black rectangular sticker featuring the text 'CRIME &amp; Vengeance' in a white, distressed, gothic-style font."
+"To the left of the text, a purple butterfly decal is attached to the side of the bowl."
+"In the background to the left, a clear plastic bag filled with brown, bread-like items is visible, along with a black electronic device and metal shelving."
+"To the right, a glass display case is partially visible."
 **Refining and combining:**
-Make it flow better. Ensure spatial relationships are clear.
-"A large, glossy red bowl dominates the foreground, resting on a dark, speckled countertop. Inside the bowl sits a bunch of yellow bananas with brown stems, leaning slightly toward the right side. The bananas have small white stickers on their skins. The exterior of the red bowl features a black rectangular decal on the front with the white text 'CRIME &amp; Vengeance' in a stylized, gothic font, and a purple butterfly sticker is affixed to the left side of the bowl. In the background to the left, a clear plastic bag filled with what appears to be bread or pastries sits next to a black electronic device and metal racks. To the right, a glass display case is partially visible, reflecting the ambient light."
+Make it flow better. Ensure specific details are included.
+"A large, glossy red bowl sits on a dark, speckled countertop, filled with a bunch of yellow bananas. The bananas, which have green-tipped stems, are clustered together with their tips pointing upward and slightly to the left; small white stickers are visible on the fruit. The exterior of the bowl features two distinct decals: on the front, a black rectangular sticker displays the text 'CRIME &amp; Vengeance' in a white, distressed, gothic-style font, and to the left of the text, a purple butterfly decal is affixed to the side. To the left of the bowl, a clear plastic bag containing what appears to be bread or pastries sits near a black electronic device and metal racks. In the background to the right, a glass display case is partially visible."
 Check against constraints:
 - Single detailed factual caption? Yes.
 - Main subject first? Yes.
@@ -5401,9 +5502,10 @@
 - No speculation? Yes.
 - No bullet points? Yes.
 Final Polish:
-"A large, glossy red bowl sits centrally in the foreground on a dark, speckled countertop, filled with a bunch of yellow bananas. The bananas, which have brown stems and small white stickers on their skins, are clustered together and lean slightly to the right. The bowl features a black rectangular decal on its front face displaying the white text 'CRIME &amp; Vengeance' in a stylized, gothic font, with a purple butterfly sticker attached to the left side of the bowl. To the left of the bowl, a clear plastic bag containing brown, bread-like items is visible near a black electronic device and metal shelving. In the background to the right, a glass display case reflects the surroundings."
-Looks good.
-A large, glossy red bowl sits centrally in the foreground on a dark, speckled countertop, filled with a bunch of yellow bananas. The bananas, which have brown stems and small white stickers on their skins, are clustered together and lean slightly to the right. The bowl features a black rectangular decal on its front face displaying the white text "CRIME &amp; Vengeance" in a stylized, gothic font, with a purple butterfly</t>
+"A large, glossy red bowl sits centrally on a dark, speckled countertop, containing a bunch of yellow bananas with green stems. The bananas are clustered together, resting inside the bowl with their tips pointing upward and slightly to the left, and small white stickers are visible on the fruit. The exterior of the bowl features two distinct decals: on the front, a black rectangular sticker displays the text 'CRIME &amp; Vengeance' in a white, distressed, gothic-style font, and to the left of the text, a purple butterfly decal is affixed to the side. To the left of the bowl, a clear plastic bag containing what appears to be bread or pastries sits near a black electronic device and metal racks. In the background to the right, a glass display case is partially visible."
+Wait, looking closer at the text, it says "CRIME &amp; Vengeance". The ampersand is stylized.
+Looking at the butterfly, it's purple with black outlines.
+Looking at the background left, there's a</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -5418,7 +5520,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -5433,12 +5535,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -5448,42 +5550,42 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.8116</t>
+          <t>0.8066</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.3301</t>
+          <t>1.3282</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.7561</t>
+          <t>0.7713</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.2886</t>
+          <t>0.2747</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.1393</t>
+          <t>0.1396</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.2172</t>
+          <t>0.2201</t>
         </is>
       </c>
     </row>
@@ -5584,7 +5686,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The model output accurately describes the key elements such as the solar-powered garden light, the starburst light pattern, the concrete path, the utility cover, and the surrounding environment. However, it introduces minor inaccuracies like mentioning 'sparse grass' instead of 'dried grass' and describing the utility cover as having a 'star design' rather than being round. The description also misses some details mentioned in the reference, such as the decorative rocks being mostly out of view.</t>
+          <t>The model output accurately describes the key elements such as the solar-powered garden light, the radial pattern of light, the concrete walkway, the utility cover, and the surrounding rocks and bush. However, it incorrectly identifies the utility cover as a 'meter' instead of a 'sewage cap,' and mentions a 'starburst-like' pattern instead of a 'diamond-shaped kaleidoscopic pattern.'</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5636,12 +5738,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>The model accurately identifies and describes the main light, its effect, the concrete path, the manhole cover, and the rocks. It hallucinates 'purple flowers' and 'sparse grass' which are not clearly visible or present in the image/reference, and misidentifies the 'garden bed' as 'dark earth' instead of 'dried grass yard'.</t>
+          <t>The model accurately identifies the main subject, its effect, and most surrounding elements. It correctly describes the light pattern, the utility cover, and the general setting. The only minor inaccuracy is describing the 'dried grass yard' as 'dark soil' and the 'sewage cap' as a 'utility meter cover', though 'utility meter cover' is a reasonable inference given the text 'METER'. The model also misses the 'dried grass' aspect of the yard.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -5688,7 +5790,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>The model's description accurately captures the main subject, the solar-powered garden light, and its effect on the surrounding area. It also correctly identifies the manhole cover and the bush in the background, although some details like the color of the bush and flowers are not entirely accurate.</t>
+          <t>The model's description accurately captures the main elements of the image, including the solar-powered garden light, the concrete path, and the utility meter cover. However, it contains some minor inaccuracies and omissions, such as not fully describing the 'diamond-shaped kaleidoscopic pattern' mentioned in the reference.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5740,7 +5842,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>The model output accurately describes the monarch butterfly, the purple flower, the hand interacting with the butterfly, and the surrounding greenery. However, it incorrectly mentions a yellow flower in the lower right corner, which is not present in the image or reference. The description is otherwise detailed and coherent.</t>
+          <t>The model output accurately describes the monarch butterfly, the purple flower, the hand's position, and the surrounding greenery. However, it incorrectly states the hand is 'holding' the butterfly's wings instead of just being near them. The description also misses mentioning the yellow flower in the bottom right corner.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5792,7 +5894,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>The model accurately describes the butterfly, the hand's interaction, the vegetation, and the background pavement. It correctly identifies the butterfly's colors and patterns, the hand's position, and the presence of various plants and flowers, including the yellow one. The only minor inaccuracy is stating the hand 'gently making contact with the butterfly and the flower' when the reference specifies 'holding its wings'.</t>
+          <t>The model accurately describes the monarch butterfly, the purple flowers, the green vegetation, and the paved surface. It correctly identifies the hand's position and interaction with the butterfly. The only minor inaccuracy is stating the hand is 'appearing to hover or make light contact' when the reference and image clearly show it holding the wings.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5844,7 +5946,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>The model's caption accurately describes the main subject (Monarch butterfly on a purple flower) and the presence of a human hand. However, it slightly misrepresents the hand's action as 'gently making contact' when the image shows the hand is not touching the butterfly. The description is mostly faithful to the image but contains minor inaccuracies.</t>
+          <t>The model's caption accurately describes the main subject (Monarch butterfly on purple flowers) and the human hand reaching towards it, but slightly misrepresents the interaction as 'hovering or making light contact' when the reference indicates the hand is 'holding its wings'. The description is generally faithful to the image but contains minor inaccuracies.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -5896,7 +5998,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>The model output contains several inaccuracies compared to the image and reference. It mentions a wooden table with tapered legs and additional objects like a black bag and a Monopoly box, which are not present in the image or reference. The reference specifies a high-angle close-up with a square wooden table and a plastic cover behind the record player, none of which are mentioned in the model output.</t>
+          <t>The model output contains several inaccuracies and hallucinations compared to the image and reference. For example, it mentions a Monopoly box and other items under the table, which are not present in the image or reference. Additionally, it incorrectly describes the background and surrounding objects.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -5911,7 +6013,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -5948,22 +6050,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>The model output accurately identifies the main objects and their attributes, such as the turntable brand, the record label, and the album cover details. However, it hallucinates the needle being on the starting point of the record and misidentifies the gold mask as red text and a gold mask, when it's a stylized face. It also misses the metal poles and the specific flooring details mentioned in the reference.</t>
+          <t>The model accurately identifies the main subjects (turntable, record, album cover) and their key attributes, including brand names and album titles. It also correctly describes the setting and several background elements. The only minor inaccuracy is stating the record label displays 'STYX in red text' when it's actually blue/purple and part of the album art.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -5978,7 +6080,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6102,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>The model output accurately describes the main elements of the image, including the black Audio-Technica turntable, the vinyl record with the label 'STYX', and the album cover 'Kilroy Was Here' leaning against the stand. However, it includes some details not present in the reference, such as the 'light brown wooden table with tapered legs' and 'a metal shelving unit holds a box of Monopoly', which are not mentioned in the reference.</t>
+          <t>The model output describes a black Audio-Technica turntable with a vinyl record labeled 'STYX' and an album cover 'Kilroy Was Here' by Styx next to it, on a wooden table. The reference description mentions a black record player on a small square wooden table with a record labeled 'STYX' and an LP record cover to its right. The model output matches the main elements described in the reference, but omits some details like the needle's position and the floor's appearance.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -6020,7 +6122,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -6052,7 +6154,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>The model output contains several inaccuracies compared to the image and reference. It incorrectly identifies the cars as Porsche 356s instead of Porsche 911s and misrepresents their colors and details. Additionally, it misses key elements like the shadow of the poster and the long rectangular-shaped shade.</t>
+          <t>The model output incorrectly identifies the cars as Porsche 356s instead of Porsche 911s and misses several key details such as the specific colors and features of the cars in the poster. Additionally, it inaccurately describes the number of cars and their positions.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -6067,7 +6169,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -6104,7 +6206,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>The model accurately identifies the main subjects (framed photo, toy cars) and many details within them, such as the water droplets, logos, and colors. However, it misidentifies the cars in the photo as Porsche 356s when the reference states Porsche 911s, and misses some specific details about the toy cars' colors and the shadow on the wall.</t>
+          <t>The model accurately identifies the main subject, the cars, and the setting. It correctly notes the water droplets, golden light, and specific logos. However, it misidentifies the cars as Porsche 356s instead of 911s and misses some details about the toy cars and the shadow mentioned in the reference.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -6156,12 +6258,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>The model output describes a large framed photograph of vintage Porsche 356 cars on a white wall, with three small toy cars below it. The reference indicates the image is of Porsche 911s, not 356s, and provides more detailed descriptions of the cars and setting.</t>
+          <t>The model output accurately describes the main elements of the image, including the large framed photograph of vintage Porsche cars and the three toy cars below it. However, there are some discrepancies in the details, such as the model describing the cars as 'Porsche 356' instead of 'Porsche 911s' as mentioned in the reference.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -6208,7 +6310,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>The model output accurately describes the rock's shape, color, and the text 'You rock!' with white paint. However, it misses the detail about the chipped paint revealing the natural color of the stone, which is mentioned in the reference. The description is coherent and specific but lacks this important detail.</t>
+          <t>The model output accurately describes the rock's shape, color, text, and decorations, matching the reference and image. However, it incorrectly states the location of the chipped paint. The description is detailed and coherent.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6260,12 +6362,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>The model accurately describes the main subject, its color, text, and the background. It misses the detail about the chipped paint mentioned in the reference, which is a minor omission.</t>
+          <t>The model accurately describes all elements present in the image and reference, including the rock's color, shape, text, decorative elements, chipped paint, and the surrounding grass. It correctly identifies the location of the chipped paint.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -6275,12 +6377,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6290,7 +6392,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -6312,7 +6414,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>The model's description accurately captures the main subject, a purple painted rock with 'You rock!' written on it, placed on grass. However, it misses the detail about the paint being chipped off above the 'U' in 'YOU', which is mentioned in the reference.</t>
+          <t>The model's description accurately captures the main subject, a purple-painted rock with 'You rock!' written on it, placed in grass. It includes most details like the rock's shape, paint chipping, and the grass's condition, but slightly misplaces the chipped paint area.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6364,7 +6466,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>The model output accurately describes the central elements of the image, such as the white bench with the word 'LOVE' in colorful letters and the mural with radiating stripes. However, it incorrectly describes the letters as 'bold and slightly rounded' instead of 'slightly overlapping' and 'chromatic aberration-like'. The description also misses the corrugated metal wall and the specific colors of the letters.</t>
+          <t>The model output accurately describes the cloud-shaped bench with 'love' written in colorful letters and the mural behind it. However, it incorrectly describes the mural's sunburst pattern as stripes instead of geometric sun beams. The description also misses the corrugated metal texture of the wall.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -6416,7 +6518,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>The model accurately describes the main elements and their relationships. It correctly identifies the 'LOVE' sculpture, its cloud-like form, the colorful letters, the background mural, and the '600' sign. The only minor inaccuracy is describing the letters as having 'vertical stripes' when the reference notes a 'chromatic aberration-like effect' and the image shows overlapping colors rather than distinct stripes.</t>
+          <t>The model accurately describes almost all elements present in the image and reference, including the 'love' text, the cloud-shaped bench, the mural's sunburst pattern and colors, the '600' sign, and the background building and sky. The only minor inaccuracy is describing the 'love' letters as white with colored outlines, when they are actually colored themselves with a chromatic aberration effect.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -6468,7 +6570,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>The model output accurately describes the main subject, the 'LOVE' sculpture on a cloud-shaped bench, and the background mural with radiating stripes and a black circle. However, some details like the exact colors of the 'LOVE' letters and the material of the wall are not precisely matched between the output and the reference.</t>
+          <t>The model's description accurately captures the main elements of the image, including the cloud-shaped bench, the 'love' text, and the mural background. However, there are some minor discrepancies in the description of the 'love' text's coloration and the mural's details.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -6483,12 +6585,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -6520,7 +6622,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>The model output accurately describes the key elements such as the green katydid, the tree trunk, the metal tag with '2003', and the bark texture. However, it misses mentioning the blurred background and the orientation of the insect. There are no significant hallucinations.</t>
+          <t>The model output accurately describes the key elements such as the green katydid, the tree trunk, the silver tag with '2003', and the bark texture. However, it incorrectly states the insect is facing left instead of up and slightly left, and it mentions lichen instead of just specks of color on the bark. The description is coherent and specific but contains minor inaccuracies.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -6540,7 +6642,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -6572,7 +6674,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>The model accurately describes the main subjects (katydid, tag, tree bark) and their attributes, including colors, textures, and the number on the tag. It correctly identifies the katydid's leaf-like body and long hind legs. The only minor discrepancy is that the reference states the '2003' is 'hardly seen', while the model says it's 'stamped clearly', which is a slight overstatement given the image.</t>
+          <t>The model accurately identifies all key objects and their attributes, including the katydid, tree tag with '2003', and detailed tree bark with lichen. It only slightly overstates the visibility of '2003' compared to the reference.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -6602,7 +6704,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -6624,7 +6726,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>The model's caption accurately describes the main elements of the image, including the green katydid and the metal tag with the number '2003' on the tree trunk. However, it misses some details such as the insect's orientation and the visibility of the number on the tag.</t>
+          <t>The model's caption accurately describes the main elements of the image, including the green katydid and the silver tag with '2003' on it, attached to a tree trunk. However, there are some discrepancies in the details, such as the direction the insect is facing and the visibility of the number '2003' on the tag.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -6644,7 +6746,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -6676,7 +6778,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>The model output accurately describes the key elements such as the silver spheres, their reflections, the green water, and the surrounding trees. However, it misses mentioning the artist Yayoi Kusama and the name of the artwork, 'Narcissus Garden.' The description is detailed and coherent, matching the visual elements closely.</t>
+          <t>The model output accurately describes the key elements such as the reflective silver spheres, the green water, and the surrounding trees. However, it misses mentioning the artist Yayoi Kusama and the name of the artwork, 'Narcissus Garden.' The description is detailed and coherent, matching the visual elements closely.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -6728,7 +6830,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>The model accurately describes all visible elements in the image, including the spheres, water, reflections, and surrounding environment, without any hallucinations. It captures the arrangement and appearance of the spheres and the nature of the water and background with good detail.</t>
+          <t>The model accurately describes the main elements of the image, including the reflective spheres, the green water, and the wooded setting. It correctly identifies the material of the spheres and their arrangement. The only minor omission is the specific mention of the sun shining on the middle trees in the background, as noted in the reference.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -6743,22 +6845,22 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
     </row>
@@ -6780,12 +6882,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>The model's caption accurately describes the scene, including the silver spheres, their reflections, and the surrounding environment. It correctly identifies the main elements and their relationships, with minor details such as the exact lighting conditions on the trees not being mentioned.</t>
+          <t>The model's description accurately captures the main elements of the image, including the silver spheres, the green water, and the wooded background. It also correctly notes the reflections on the spheres and the water, and the arrangement of the spheres.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -6795,7 +6897,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -6810,7 +6912,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -6832,12 +6934,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>The model output accurately describes the presence of two ships, their relative positions, and the color of the water. However, it incorrectly states the orientation of the ships and provides inaccurate details about the ships' colors and structures. The reference specifies that both ships face the top right corner, while the model describes them as facing opposite directions. Additionally, the model mentions containers and superstructures that are not evident in the image.</t>
+          <t>The model output accurately describes the presence of two ships, their relative positions, and the ocean background. However, it incorrectly states that both ships have stacked cargo containers and mentions a reddish-pink stripe and superstructure details that are not present in the image or reference. The description is coherent and covers the core elements but includes several inaccuracies.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -6884,12 +6986,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>The model accurately identifies the two ships and their general appearance, but incorrectly states the ships are facing opposite directions when both are oriented towards the top right. It also adds details like 'stacked cargo containers' and 'white superstructure' which are not clearly discernible in the image or mentioned in the reference.</t>
+          <t>The model accurately identifies the two ships, their general appearance, and their positions. It correctly notes the 'reddish-pink stripe' on the top ship and the 'grey hull' of the bottom ship, aligning with the reference. The description of the water and aerial perspective is also accurate.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -6899,12 +7001,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -6914,7 +7016,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -6936,7 +7038,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>The model's description accurately captures the main elements of the image, including the presence of two ships in the ocean and their general characteristics. However, it introduces some details not present in the reference, such as the specific orientation and cargo details.</t>
+          <t>The model's description accurately captures the main elements of the image, including the presence of two ships in the ocean and their general characteristics. However, it includes some details not present in the reference, such as the 'white superstructure' and 'diffuse lighting', which may be considered minor hallucinations.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -6988,7 +7090,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>The model output accurately describes the excavator's brand, model, and configuration, matching the image and reference. However, it incorrectly mentions a 'concrete curb' and 'silver car,' which are not prominent in the reference. The description also misses key details such as the excavator's position relative to the foundation and the lighting effects.</t>
+          <t>The model output accurately describes the excavator's brand, model, and configuration, including the grapple attachment. However, it introduces elements like a car behind a fence and a paved road that are not present in the image or reference. The description also misses key details such as the excavator's position relative to the curb and the specific lighting effects.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -7018,7 +7120,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -7040,7 +7142,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>The model accurately identifies almost all details, including specific text on the excavator. The only minor inaccuracy is 'TF100332' instead of 'TFX00332' and describing the grapple as 'resting on the ground' when it's 'resting teeth down into the soil and grass'. It also misses the detail about the excavator's treads being aligned facing the camera.</t>
+          <t>The model accurately identifies the excavator, its brand, model, and specific features like the grapple and ID number. It correctly describes the setting, lighting, and background elements, including the chain-link fence and car. The only minor inaccuracy is the ID number, which is 'TFX00332' in the image and reference, not 'TF100332'.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -7055,7 +7157,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -7070,7 +7172,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -7092,7 +7194,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>The model's caption accurately describes the Caterpillar 320E excavator, its grapple attachment, and the surrounding environment, including the dark blue sky, chain-link fence, and a car visible through it. However, there are minor discrepancies in the identification code 'TF100332' versus 'TFX00332' in the reference, and some details like the flat foundation are not mentioned.</t>
+          <t>The model output accurately describes the Caterpillar 320E excavator, its grapple attachment, and the surrounding environment, including the dark blue night sky, chain-link fence, and silver car in the background. However, there are some discrepancies in the details, such as the serial number 'TF100332' in the output versus 'TFX00332' in the reference.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -7144,12 +7246,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>The model output accurately describes the key elements such as the number of rackets, their colors, and the setting. However, it incorrectly identifies the brand 'Babolat' and mentions specific details about the brand name being visible, which contradicts the reference stating the text is illegible. The description also omits the white hinge on the door.</t>
+          <t>The model output accurately describes the key details such as the number of rackets, their colors, and their positioning. However, it incorrectly identifies the brand 'Babolat' and provides more specific details about the text on the rackets than what is visible in the image. The description also omits the white hinge on the door mentioned in the reference.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -7196,19 +7298,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>The model accurately identifies all major objects and their attributes, including the specific brand 'Babolat' and the colors of the rackets and background. It only misses a minor detail about the door hinge and the illegibility of some writing, which are very minor omissions.</t>
+          <t>The model accurately identifies the objects and their arrangement. It hallucinates the brand name 'Babolat' being visible and legible on all rackets, which the reference explicitly states is not the case. It also misses the detail of the rackets resting on their heads.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>4</t>
@@ -7216,7 +7318,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -7226,7 +7328,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -7248,7 +7350,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>The model output accurately describes the three tennis rackets, their colors, and the background elements such as the white door and the light-colored wooden floor. However, it incorrectly identifies the brand name as 'Babolat' which is not confirmed in the reference description.</t>
+          <t>The model output accurately describes the three tennis rackets, their colors, and the background elements such as the white door and the light-colored wooden floor. However, it incorrectly states that the brand name 'Babolat' is visible on the throat of the rackets, which is not supported by the reference or the image.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -7263,7 +7365,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -7278,7 +7380,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -7300,7 +7402,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>The model output accurately describes the central cow sculpture and its green grass-like base, matching the image and reference. However, it misses key details about the surrounding artworks and their specific attributes, such as the 'Guernica #3 (Resist)' and 'Smoker.' The description is coherent and specific regarding the sculpture but lacks completeness in covering all salient elements.</t>
+          <t>The model output accurately describes the central cow sculpture and its green grass-like base, matching the image and reference. However, it misses key details about the surrounding artworks and their specific attributes mentioned in the reference. The description is coherent and specific regarding the sculpture but lacks completeness.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -7320,7 +7422,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -7352,7 +7454,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>The model accurately identifies the main sculpture and its key features, as well as the general gallery setting. However, it incorrectly describes the artwork on the far right as a hand holding a cigarette, when the reference clarifies it's a hand with nail polish holding a smoking cigarette to lips, and it omits the specific details of the other artworks mentioned in the reference.</t>
+          <t>The model accurately identifies the main sculpture and its key features, as well as the surrounding artworks and gallery setting. It correctly describes the 'cutout style' of the cow and the 'grass-like spikes'. The description of the artworks on the wall is also largely accurate, though it misses some specific details mentioned in the reference.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -7362,17 +7464,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -7382,7 +7484,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7506,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>The model output accurately describes the main subject, a stylized cream-colored cow sculpture behind a bright green grass-like structure on a white plinth. It also correctly identifies the gallery setting and some of the artworks on the walls. However, there are minor inaccuracies and omissions in describing the artworks and the setting.</t>
+          <t>The model's description accurately captures the main subject, a stylized cream-colored cow sculpture behind a bright green grass-like structure on a white plinth. It also describes the gallery setting and some of the artworks on the walls, though with some omissions and minor inaccuracies.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -7456,7 +7558,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>The model output accurately describes the bridge, water, vegetation, and sky, matching the image and reference. However, it misses some details like the five vertical details at the center of the bridge and the long vertical stripe mentioned in the reference. There are no hallucinations.</t>
+          <t>The model output accurately describes the bridge, water, vegetation, and background elements, matching the image and reference. However, it misses some specific architectural details like the five vertical details at the center mentioned in the reference. The description is coherent and free from hallucinations.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -7508,12 +7610,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>The model accurately describes nearly all elements present in the image and reference, including specific details about the bridge's structure, the water, and the surrounding vegetation and distant buildings. It correctly identifies the '20' sign and the type of trees.</t>
+          <t>The model accurately describes all major elements and many minor details, such as the fluted concrete element and vertical grooves, which are present in the image and confirmed by the reference. It correctly identifies the water color, sky, trees, and distant buildings. The only minor inaccuracy is describing the water under the bridge as 'dark and shadowed' while the reference notes 'bright white blue light' in the center, but this is a subtle detail.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7560,7 +7662,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>The model's caption accurately describes the main elements of the image, including the concrete arch bridge, the murky water, the surrounding vegetation, and the distant buildings. However, it misses some specific details mentioned in the reference, such as the exact number of vertical details on the bridge and the presence of a hanging tree branch on the right bank.</t>
+          <t>The model's caption accurately describes the main elements of the image, including the concrete arch bridge, the murky water, the palm trees, and the background buildings. However, it misses some specific details mentioned in the reference, such as the bright white blue light under the bridge and the hanging tree branch on the right bank.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -7612,7 +7714,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>The model output accurately describes the neon tunnel and playing cards, but it contains inaccuracies in the card details and misses the neon line behind the cards. The description is detailed but has some hallucinations.</t>
+          <t>The model output accurately describes the glowing tunnel and playing cards, including their colors and arrangement. However, it incorrectly identifies some card values and misses the presence of the neon turquoise line with a white center behind the cards.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -7642,7 +7744,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -7664,7 +7766,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>The model accurately identifies the main elements and their general appearance but makes several errors in identifying the specific playing cards and misses some details of the tunnel and the background light strip.</t>
+          <t>The model accurately identifies the main elements and their general appearance. However, it hallucinates several card values and suits, and misses the 'small blue and yellow squares' on the tunnel and the 'white center' of the vertical line on the right, as described in the reference.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -7716,12 +7818,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>The model's description accurately captures the main elements of the image, including the neon tunnel and the playing cards, but contains some inaccuracies in the details of the cards and omits certain aspects like the specific structure of the tunnel and the neon line behind the cards.</t>
+          <t>The model's description accurately captures the main elements of the image, including the glowing rectangular tunnel and the vertical cascade of playing cards. However, there are some discrepancies in the details of the cards and the presence of a faint vertical light strip on the far right edge.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -7731,7 +7833,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -7768,22 +7870,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>The model output accurately describes many key details such as the truck's color scheme, 'Hot Wheels' branding, tire size, and undercarriage components. However, it incorrectly mentions a wooden platform and blue tape with logos instead of a blue ribbon-style barrier. The description misses some details like the exact positioning of the '68' and the specific style of the 'Hot Wheels' logo.</t>
+          <t>The model output accurately describes many key details such as the truck's vibrant colors, the 'Hot Wheels' branding, the number '68', and the large tires. However, it incorrectly mentions a wooden platform and an indoor arena setting, which are not present in the image or reference. The description misses some specific details like the chevron treads and the exact positioning of the banners.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -7798,7 +7900,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -7820,7 +7922,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>The model accurately describes nearly all visible elements of the monster truck and its surroundings, including specific colors, logos, and the background setting. It only misses a few minor details mentioned in the reference, such as the 'drippy' style of the number '68' and the specific chevron treads on the tires.</t>
+          <t>The model accurately describes the monster truck, its branding, colors, and the number '68'. It correctly identifies the massive tires, exposed suspension, and the background elements like the Hot Wheels banners, caution tape, and arena seating. The description is detailed and well-structured.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -7835,7 +7937,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -7872,12 +7974,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>The model output accurately describes the main subject, a Hot Wheels monster truck, and its details such as the red body, colorful design, 'Hot Wheels' logo, number '68', and large black tires. It also correctly identifies the background elements like the blue banners and checkered flag. However, some minor details like the exact style of the 'Hot Wheels' logo and the presence of 'Monster Trucks' text are mentioned but not entirely precise in their description.</t>
+          <t>The model output accurately describes the main subject, a 'Hot Wheels' monster truck, and its details such as the red body, 'Hot Wheels' logo, number '68', large black tires, and exposed suspension. It also correctly identifies the setting, including the blue barriers, wooden platform, and checkered flag in the background.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -7887,7 +7989,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -7902,7 +8004,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -7924,12 +8026,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>The model output accurately describes the 'Flamingo' sign and its details, such as the illuminated text and the flamingo head structure. However, it misses key elements like the circular neon artwork beneath the sign and the specific color patterns mentioned in the reference. The description also includes some inaccuracies, such as mentioning a multi-story building behind the sign instead of focusing on the entrance details.</t>
+          <t>The model output contains several inaccuracies and hallucinations compared to the image and reference. For example, it mentions a giant flamingo head structure, which is not present in the image. Additionally, it incorrectly describes the 'WAYNE' marquee as being to the right of the flamingo sign, while it is actually below the main sign. The reference provides a more accurate and detailed description.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -7976,7 +8078,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>The model accurately identifies the main sign and its details, the background building, and the 'WAYNE' sign. However, it hallucinates 'THE COSMOPOLITAN' text on the building and misinterprets the flamingo head structure, which is actually a floral/petal design. The description also cuts off abruptly.</t>
+          <t>The model hallucinates a 'flamingo head' structure for the main neon artwork, which is actually a floral/petal design. It also incorrectly identifies reversed text on the building as 'THE COSMOPOLITAN' when it's not clearly legible and not mentioned in the reference.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -7986,12 +8088,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -8028,7 +8130,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>The model output accurately describes the main elements of the image, including the Flamingo sign, the hotel building, and the surrounding details. However, it contains some minor inaccuracies and omissions compared to the reference description.</t>
+          <t>The model's description accurately captures the main subject, the Flamingo sign, and its details. However, it misses some specifics like the 'petal-like' structure of the neon artwork and the exact colors of the neon bars.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -8048,7 +8150,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -8080,7 +8182,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>The model output correctly identifies the numbers 3, 2, and 1 on the floor, their arrangement, and the presence of a black box and a wooden circle with a black metal piece. However, it incorrectly describes the box as green instead of black and adds unnecessary details about yellow dots and white markings. The description of the floor as grey concrete is accurate.</t>
+          <t>The model output correctly identifies the numbers 3 and 2 along with their positions relative to each other, but it misses the presence of the number 1 and the hash marks mentioned in the reference. Additionally, it introduces irrelevant details such as a green box and wooden spool that are not present in the image or reference.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -8095,7 +8197,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -8132,12 +8234,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>The model accurately identifies the numbers and their markings, the concrete floor, and the objects at the top. It correctly notes the '1' is faint and describes it as a vertical line, which aligns with the reference's 'partially rubbed off but still visible'. The model's description of the box as 'dark green' differs from the reference's 'black box', which is a minor inaccuracy.</t>
+          <t>The model accurately identifies the numbers 3 and 2 and their hash marks, as well as the green box and wooden spool. However, it misses the number '1' entirely, which is a significant omission, and hallucinates a 'black cable' on the spool when the reference states a 'black metal piece'.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -8147,7 +8249,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -8184,27 +8286,27 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>The model output accurately describes the numbers 3, 2, and 1 on the floor, along with the surrounding objects like the dark green box and the wooden spool with a black handle. However, there are some minor inaccuracies and omissions in the description, such as not explicitly mentioning that the numbers are written underneath hash marks or that the '1' is partially rubbed off.</t>
+          <t>The model output accurately describes the numbers '3' and '2' on the floor, the presence of a mark above them, and the objects in the top corners, but it misses the number '1' on the right and misdescribes some details like the box and the wooden spool. The description is mostly coherent and specific but has some inaccuracies.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -8236,7 +8338,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>The model output accurately describes the silhouettes, wall color, and vertical seams, but misses key details such as the diagonal angle of the wall, the specific poses indicating one person falling and the other reaching out, and the presence of a light switch. The description of the red glow is accurate but lacks precision compared to the reference.</t>
+          <t>The model output accurately describes the silhouettes and their poses, the wall's color, and the presence of vertical seams. However, it misses key details such as the diagonal angle of the wall, the specific clothing styles, and the red light above the left figure's arms. The description also introduces a 'reddish glow' and a 'dark horizontal structure' that are not mentioned in the reference.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -8288,7 +8390,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>The model accurately describes the two silhouettes, their poses, and the wall's color and texture. It misses some minor details like the 'light switch' and 'muted white lights' mentioned in the reference, and misinterprets the red light's position slightly.</t>
+          <t>The model accurately describes the two silhouettes and their poses, the wall's color and seams, and the general lighting. However, it misinterprets the 'falling' action of the right figure as 'kicking or leaping' and misses the 'other muted white lights' mentioned in the reference.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -8340,7 +8442,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>The model's description accurately captures the main elements of the image, including the silhouettes, their poses, and the wall's color and features. However, it misses some details like the clothing styles and the light switch on the wall.</t>
+          <t>The model's description accurately captures the main elements of the image, including the silhouettes, their poses, and the wall's characteristics. However, it introduces some minor inaccuracies and omits a few details present in the reference.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -8360,7 +8462,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -8392,12 +8494,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>The model output accurately describes the spider's appearance and position, the surface it is on, and the background elements. However, it misses details about the spider's movement direction and the specific type of spider. The description is coherent and specific, but lacks some completeness compared to the reference.</t>
+          <t>The model output accurately describes the spider's features, such as its round abdomen, leg patterns, and positioning, as well as the surface texture and background elements. However, it incorrectly identifies the surface as a wooden beam instead of a tile and mentions a concrete edge with a circular hole, which is not present in the image.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -8444,27 +8546,27 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>The model accurately describes the spider, the tile, and the background elements, including the specific details of the spider's appearance and the texture of the tile. It correctly identifies the 'circular indentation' as a drainage pipe and the 'white wall' as vinyl siding, aligning well with the reference.</t>
+          <t>The model accurately describes the spider and the surface it's on, including details like the leg banding and surface texture. It correctly identifies the background elements like foliage and white siding, though it misidentifies the 'drainage pipe' as a 'circular hole or indentation' and the 'tile' as a 'wooden beam'.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -8474,7 +8576,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -8496,7 +8598,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>The model's description accurately captures the main subject (spider), its attributes (brown abdomen, banded legs), and the surface it's on (reddish-brown tile). It also mentions the background elements (green foliage, white wall, dark beam). However, some details like the spider's movement direction and specific patterns on the abdomen are not mentioned.</t>
+          <t>The model's description accurately captures the main subject, a spider on a reddish-brown surface, and includes details about its appearance and the background. However, there are some discrepancies in the description of the surface and the spider's direction.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -8516,7 +8618,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -8548,17 +8650,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>The model output accurately describes the red bowl with bananas, including the stickers and surrounding objects. However, it incorrectly states the text as 'CRIME &amp; Vengeance' instead of 'CRIME REVENGE', and misses some details like the metallic rack and the clear partition mentioned in the reference.</t>
+          <t>The model output accurately describes the red bowl with bananas, including the stickers ('CRIME REVENGE' and the purple butterfly), but incorrectly states the text as 'CRIME &amp; Vengeance'. It also includes irrelevant details about a plastic bag, bread, and a glass display case that are not present in the image or reference.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8578,7 +8680,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -8600,7 +8702,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>The model accurately describes the main subjects (bowl, bananas) and their key attributes, including the text on the bowl. However, it misidentifies 'REVENGE' as 'Vengeance' and misses some background details like the metallic-reinforced menu corners and the clear partition with water stains.</t>
+          <t>The model accurately describes the main subjects and many details, but misidentifies the text on the bowl as 'CRIME &amp; Vengeance' instead of 'CRIME REVENGE' and misses some background details like the diner-style menu and clear partition.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -8652,7 +8754,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>The model output accurately describes the main subject, a red bowl with bananas and stickers, but contains minor inaccuracies and omissions compared to the reference description. The output correctly identifies the bowl, bananas, and stickers but misinterprets some background elements.</t>
+          <t>The model's caption accurately describes the main subject, a red bowl with bananas and stickers, but contains minor inaccuracies and omissions compared to the reference description. The caption correctly identifies the bowl, bananas, and stickers but misses some details like the exact text on the sticker and background elements.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -8672,7 +8774,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -8682,7 +8784,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
